--- a/data/AIRSPACE_線下通路_行銷排程_含甘特圖_2025-2026.xlsx
+++ b/data/AIRSPACE_線下通路_行銷排程_含甘特圖_2025-2026.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="510" yWindow="570" windowWidth="27735" windowHeight="10800"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="行銷排程" sheetId="1" r:id="rId5"/>
+    <sheet name="行銷排程" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'行銷排程'!$A$1:$I$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">行銷排程!$A$1:$I$152</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="457">
   <si>
     <t>年度</t>
   </si>
@@ -32,28 +36,30 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
       </rPr>
       <t>適用門市</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="微軟正黑體"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <family val="2"/>
+        <charset val="136"/>
       </rPr>
       <t>/</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
       </rPr>
       <t>通路</t>
     </r>
@@ -1329,41 +1335,151 @@
   </si>
   <si>
     <t>6/5-6/21  全館商品三件以上85折 部分百貨店櫃配合百貨年中慶提前至6/5開跑 適用百貨 新台南FOCUS店</t>
+  </si>
+  <si>
+    <t>6/8-6/21 門網同步 (部分百貨店櫃提前開跑) 全館商品三件以上85折</t>
+  </si>
+  <si>
+    <t>小碼聯名IP全系列/大小碼26年KOL聯名/大碼W21 KT聯名商品、湯姆貓聯名商品 / 甜甜價/體驗價/組合價(包含買單件)/開運價/出清品;不列入折扣活動</t>
+  </si>
+  <si>
+    <t>2026/06/10郵件</t>
+  </si>
+  <si>
+    <t>6/11-6/28</t>
+  </si>
+  <si>
+    <t>6/11-6/28 門市提前開跑 全館消費滿2500贈湯姆貓手機支架 (可不含聯名商品，隨機贈送不挑款，不累贈) 全館消費任一商品可$290加購湯姆貓手機支架 (不單賣只可加購/滿額贈) 全館消費任一商品可$490加購湯姆貓手機鍊 (不單賣只可加購) 凡購買湯姆貓聯名商品贈湯姆貓不織布袋 (可累贈，若購買兩件湯姆貓商品則贈兩個，以此類推) [image: image.png]</t>
+  </si>
+  <si>
+    <t>湯姆貓聯名可於6/11上架販售，贈品活動同步提前開跑;如消費滿2500且加購手機支架，則KEY入兩個贈品，系統會自動判斷一個為加購價/一個為贈品;請務必確實銷貨，若有漏KEY，可另外成立一單備註補XX單之贈品;贈不織布袋及手機鍊僅販售CA及PLUS及IP店櫃適用活動，贈手機支架全體正價店適用</t>
+  </si>
+  <si>
+    <t>活動貨組如附件</t>
+  </si>
+  <si>
+    <t>2026/06/15郵件</t>
+  </si>
+  <si>
+    <t>6/29起</t>
+  </si>
+  <si>
+    <t>6/29起新增 門市品牌活動</t>
+  </si>
+  <si>
+    <t>2026/06/18郵件</t>
+  </si>
+  <si>
+    <t>8/1起 官網下單門市取貨獨家 凡於官網下單門市取貨者 當日到店取貨且在門市不限消費金額現折100 POS操作：輸入會員條碼→再輸入折扣碼【PICKUP100】</t>
+  </si>
+  <si>
+    <t>2026/06/30郵件</t>
+  </si>
+  <si>
+    <t>6/29起 門市獨家 VIP/SVIP於正價店凡消費即可加贈品牌紙袋 (一個筆單贈送乙個) 凡消費泳裝品項即可加贈品牌提袋 (一個商品贈送乙個，如買兩件即可贈2個)</t>
+  </si>
+  <si>
+    <t>7/13-7/26</t>
+  </si>
+  <si>
+    <t>全館單件95折、兩件88折、三件85折</t>
+  </si>
+  <si>
+    <t>IP商品/甜甜價/體驗價/組合價(包含買單件)*不列入折扣活動</t>
+  </si>
+  <si>
+    <t>7/9-7/26</t>
+  </si>
+  <si>
+    <t>7/9-7/26 部分店櫃適用 一般會員/過路客滿3200贈玩總行李吊牌 VIP/SVIP滿2500贈玩總行李吊牌 左營新光店、台中漢神店、嘉義秀泰店、新台南FOCUS店 [image: image.png]</t>
+  </si>
+  <si>
+    <t>台中漢神</t>
+  </si>
+  <si>
+    <t>適用店櫃：南西IP店、夢時代IP店、 新莊宏匯店、 桃園統領店;臨櫃及員購滿額贈門檻金額為3200</t>
+  </si>
+  <si>
+    <t>7/6-7/12</t>
+  </si>
+  <si>
+    <t>7/6-7/12 IP專賣店櫃獨家 消費DINOTAENG商品即贈DINOTAENG滑鼠墊 全館滿2500贈DINOTAENG手機鍊 [image: image.png]</t>
+  </si>
+  <si>
+    <t>7/13-7/26 IP專賣店櫃獨家 消費DINOTAENG商品即贈DINOTAENG手機支架 [image: image.png]</t>
+  </si>
+  <si>
+    <t>7/9-7/12</t>
+  </si>
+  <si>
+    <t>會員專屬</t>
+  </si>
+  <si>
+    <t>情境說明 若於7/9-7/12 之間VIP/SVIP消費滿2500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d"/>
+    <numFmt numFmtId="176" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Noto Sans"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1372,7 +1488,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1424,7 +1540,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFDDDDDD"/>
@@ -1438,154 +1560,193 @@
       <bottom style="thin">
         <color rgb="FFDDDDDD"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="15">
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEEBF7"/>
+          <bgColor rgb="FFDEEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDEDED"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFF2CC"/>
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDEDED"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEEBF7"/>
+          <bgColor rgb="FFDEEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDEEBF7"/>
-          <bgColor rgb="FFDEEBF7"/>
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE2EFDA"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FFF8CBAD"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEDEDED"/>
-          <bgColor rgb="FFEDEDED"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1593,7 +1754,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1783,27 +1944,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="6.0"/>
-    <col customWidth="1" min="3" max="4" width="16.0"/>
-    <col customWidth="1" min="5" max="5" width="61.71"/>
-    <col customWidth="1" min="6" max="6" width="22.0"/>
-    <col customWidth="1" min="7" max="7" width="14.0"/>
-    <col customWidth="1" min="8" max="8" width="62.71"/>
-    <col customWidth="1" min="9" max="9" width="22.0"/>
-    <col customWidth="1" min="10" max="26" width="8.71"/>
+    <col min="1" max="2" width="6" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="61.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="62.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1832,9 +1993,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
@@ -1861,9 +2022,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" ht="28.5">
       <c r="A3" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
@@ -1890,9 +2051,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" ht="28.5">
       <c r="A4" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -1919,9 +2080,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" ht="27">
       <c r="A5" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1948,9 +2109,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" ht="54">
       <c r="A6" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
@@ -1977,9 +2138,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" ht="71.25">
       <c r="A7" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
@@ -2006,9 +2167,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" ht="71.25">
       <c r="A8" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
@@ -2035,9 +2196,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>39</v>
@@ -2064,9 +2225,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9">
       <c r="A10" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>39</v>
@@ -2093,9 +2254,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" ht="67.5">
       <c r="A11" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>39</v>
@@ -2122,15 +2283,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9">
       <c r="A12" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="9">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>48</v>
@@ -2151,9 +2312,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" ht="27">
       <c r="A13" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>39</v>
@@ -2180,9 +2341,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" ht="27">
       <c r="A14" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>39</v>
@@ -2209,9 +2370,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" ht="71.25">
       <c r="A15" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>39</v>
@@ -2238,9 +2399,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9">
       <c r="A16" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>61</v>
@@ -2267,9 +2428,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9">
       <c r="A17" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>61</v>
@@ -2296,9 +2457,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" ht="28.5">
       <c r="A18" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>61</v>
@@ -2325,9 +2486,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9">
       <c r="A19" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>61</v>
@@ -2354,9 +2515,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9" ht="42.75">
       <c r="A20" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>61</v>
@@ -2383,9 +2544,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>61</v>
@@ -2412,9 +2573,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>76</v>
@@ -2441,9 +2602,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>76</v>
@@ -2470,9 +2631,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>76</v>
@@ -2499,9 +2660,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>76</v>
@@ -2528,9 +2689,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>76</v>
@@ -2557,9 +2718,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>91</v>
@@ -2586,9 +2747,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>91</v>
@@ -2615,9 +2776,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>91</v>
@@ -2644,9 +2805,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>91</v>
@@ -2673,9 +2834,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>91</v>
@@ -2702,9 +2863,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>104</v>
@@ -2731,9 +2892,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1">
       <c r="A33" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>104</v>
@@ -2760,9 +2921,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1">
       <c r="A34" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>104</v>
@@ -2789,9 +2950,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1">
       <c r="A35" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>104</v>
@@ -2818,9 +2979,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1">
       <c r="A36" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>104</v>
@@ -2847,9 +3008,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1">
       <c r="A37" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>104</v>
@@ -2876,9 +3037,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:9" ht="15.75" customHeight="1">
       <c r="A38" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>104</v>
@@ -2905,9 +3066,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1">
       <c r="A39" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>123</v>
@@ -2934,9 +3095,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1">
       <c r="A40" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>123</v>
@@ -2963,9 +3124,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1">
       <c r="A41" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>123</v>
@@ -2992,9 +3153,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1">
       <c r="A42" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>123</v>
@@ -3021,9 +3182,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1">
       <c r="A43" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>123</v>
@@ -3050,9 +3211,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1">
       <c r="A44" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>123</v>
@@ -3079,9 +3240,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1">
       <c r="A45" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>136</v>
@@ -3108,9 +3269,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1">
       <c r="A46" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>136</v>
@@ -3137,9 +3298,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1">
       <c r="A47" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>136</v>
@@ -3166,9 +3327,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1">
       <c r="A48" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>136</v>
@@ -3195,9 +3356,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:9" ht="15.75" customHeight="1">
       <c r="A49" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>136</v>
@@ -3224,9 +3385,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:9" ht="15.75" customHeight="1">
       <c r="A50" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>136</v>
@@ -3253,9 +3414,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:9" ht="15.75" customHeight="1">
       <c r="A51" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>136</v>
@@ -3282,9 +3443,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:9" ht="15.75" customHeight="1">
       <c r="A52" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>136</v>
@@ -3311,9 +3472,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:9" ht="15.75" customHeight="1">
       <c r="A53" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>136</v>
@@ -3340,9 +3501,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:9" ht="15.75" customHeight="1">
       <c r="A54" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>165</v>
@@ -3369,9 +3530,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:9" ht="15.75" customHeight="1">
       <c r="A55" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>165</v>
@@ -3398,9 +3559,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:9" ht="15.75" customHeight="1">
       <c r="A56" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>165</v>
@@ -3427,9 +3588,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:9" ht="15.75" customHeight="1">
       <c r="A57" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>165</v>
@@ -3456,9 +3617,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:9" ht="15.75" customHeight="1">
       <c r="A58" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>165</v>
@@ -3485,9 +3646,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:9" ht="15.75" customHeight="1">
       <c r="A59" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>165</v>
@@ -3514,9 +3675,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:9" ht="15.75" customHeight="1">
       <c r="A60" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>184</v>
@@ -3543,9 +3704,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:9" ht="15.75" customHeight="1">
       <c r="A61" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>184</v>
@@ -3572,9 +3733,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:9" ht="15.75" customHeight="1">
       <c r="A62" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>184</v>
@@ -3601,9 +3762,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:9" ht="15.75" customHeight="1">
       <c r="A63" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>184</v>
@@ -3630,9 +3791,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:9" ht="15.75" customHeight="1">
       <c r="A64" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>184</v>
@@ -3659,9 +3820,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:9" ht="15.75" customHeight="1">
       <c r="A65" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>184</v>
@@ -3688,9 +3849,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:9" ht="15.75" customHeight="1">
       <c r="A66" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>184</v>
@@ -3717,9 +3878,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:9" ht="15.75" customHeight="1">
       <c r="A67" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>203</v>
@@ -3746,9 +3907,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:9" ht="15.75" customHeight="1">
       <c r="A68" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>203</v>
@@ -3775,9 +3936,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:9" ht="15.75" customHeight="1">
       <c r="A69" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>203</v>
@@ -3804,9 +3965,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:9" ht="15.75" customHeight="1">
       <c r="A70" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>203</v>
@@ -3833,9 +3994,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:9" ht="15.75" customHeight="1">
       <c r="A71" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>203</v>
@@ -3862,9 +4023,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:9" ht="15.75" customHeight="1">
       <c r="A72" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>203</v>
@@ -3891,9 +4052,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:9" ht="15.75" customHeight="1">
       <c r="A73" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>203</v>
@@ -3920,9 +4081,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:9" ht="15.75" customHeight="1">
       <c r="A74" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>222</v>
@@ -3949,9 +4110,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:9" ht="15.75" customHeight="1">
       <c r="A75" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>222</v>
@@ -3978,9 +4139,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:9" ht="15.75" customHeight="1">
       <c r="A76" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>222</v>
@@ -4007,9 +4168,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:9" ht="15.75" customHeight="1">
       <c r="A77" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>222</v>
@@ -4036,15 +4197,15 @@
         <v>223</v>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:9" ht="15.75" customHeight="1">
       <c r="A78" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>222</v>
       </c>
       <c r="C78" s="9">
-        <v>46381.0</v>
+        <v>46381</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>232</v>
@@ -4065,9 +4226,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:9" ht="15.75" customHeight="1">
       <c r="A79" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>222</v>
@@ -4094,9 +4255,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:9" ht="15.75" customHeight="1">
       <c r="A80" s="2">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>222</v>
@@ -4123,9 +4284,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:9" ht="15.75" customHeight="1">
       <c r="A81" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>9</v>
@@ -4152,9 +4313,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:9" ht="15.75" customHeight="1">
       <c r="A82" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>9</v>
@@ -4181,9 +4342,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:9" ht="15.75" customHeight="1">
       <c r="A83" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>9</v>
@@ -4210,9 +4371,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:9" ht="15.75" customHeight="1">
       <c r="A84" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>9</v>
@@ -4239,9 +4400,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:9" ht="15.75" customHeight="1">
       <c r="A85" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>9</v>
@@ -4268,9 +4429,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:9" ht="15.75" customHeight="1">
       <c r="A86" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>9</v>
@@ -4297,9 +4458,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:9" ht="15.75" customHeight="1">
       <c r="A87" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>9</v>
@@ -4326,9 +4487,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:9" ht="15.75" customHeight="1">
       <c r="A88" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>9</v>
@@ -4355,9 +4516,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:9" ht="15.75" customHeight="1">
       <c r="A89" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>9</v>
@@ -4384,9 +4545,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:9" ht="15.75" customHeight="1">
       <c r="A90" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>9</v>
@@ -4413,9 +4574,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:9" ht="15.75" customHeight="1">
       <c r="A91" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>9</v>
@@ -4442,9 +4603,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:9" ht="15.75" customHeight="1">
       <c r="A92" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>9</v>
@@ -4471,9 +4632,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:9" ht="15.75" customHeight="1">
       <c r="A93" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>9</v>
@@ -4500,9 +4661,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:9" ht="15.75" customHeight="1">
       <c r="A94" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>39</v>
@@ -4529,9 +4690,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:9" ht="15.75" customHeight="1">
       <c r="A95" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>39</v>
@@ -4558,9 +4719,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:9" ht="15.75" customHeight="1">
       <c r="A96" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>39</v>
@@ -4587,9 +4748,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:9" ht="15.75" customHeight="1">
       <c r="A97" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>39</v>
@@ -4616,9 +4777,9 @@
         <v>290</v>
       </c>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:9" ht="15.75" customHeight="1">
       <c r="A98" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>39</v>
@@ -4645,9 +4806,9 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:9" ht="15.75" customHeight="1">
       <c r="A99" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>39</v>
@@ -4674,9 +4835,9 @@
         <v>299</v>
       </c>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:9" ht="15.75" customHeight="1">
       <c r="A100" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>39</v>
@@ -4703,9 +4864,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:9" ht="15.75" customHeight="1">
       <c r="A101" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>39</v>
@@ -4732,9 +4893,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:9" ht="15.75" customHeight="1">
       <c r="A102" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>39</v>
@@ -4761,9 +4922,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:9" ht="15.75" customHeight="1">
       <c r="A103" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>61</v>
@@ -4790,9 +4951,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:9" ht="15.75" customHeight="1">
       <c r="A104" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>61</v>
@@ -4819,9 +4980,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:9" ht="15.75" customHeight="1">
       <c r="A105" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>61</v>
@@ -4848,9 +5009,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:9" ht="15.75" customHeight="1">
       <c r="A106" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>61</v>
@@ -4877,9 +5038,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:9" ht="15.75" customHeight="1">
       <c r="A107" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>61</v>
@@ -4906,9 +5067,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:9" ht="15.75" customHeight="1">
       <c r="A108" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>61</v>
@@ -4935,9 +5096,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:9" ht="15.75" customHeight="1">
       <c r="A109" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>61</v>
@@ -4964,9 +5125,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:9" ht="15.75" customHeight="1">
       <c r="A110" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>61</v>
@@ -4993,9 +5154,9 @@
         <v>331</v>
       </c>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:9" ht="15.75" customHeight="1">
       <c r="A111" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>61</v>
@@ -5022,9 +5183,9 @@
         <v>331</v>
       </c>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:9" ht="15.75" customHeight="1">
       <c r="A112" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>61</v>
@@ -5051,9 +5212,9 @@
         <v>335</v>
       </c>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:9" ht="15.75" customHeight="1">
       <c r="A113" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>61</v>
@@ -5080,9 +5241,9 @@
         <v>335</v>
       </c>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:9" ht="15.75" customHeight="1">
       <c r="A114" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>61</v>
@@ -5109,9 +5270,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:9" ht="15.75" customHeight="1">
       <c r="A115" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>61</v>
@@ -5138,9 +5299,9 @@
         <v>341</v>
       </c>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:9" ht="15.75" customHeight="1">
       <c r="A116" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>61</v>
@@ -5167,15 +5328,15 @@
         <v>341</v>
       </c>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:9" ht="15.75" customHeight="1">
       <c r="A117" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C117" s="9">
-        <v>46111.0</v>
+        <v>46111</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>343</v>
@@ -5196,9 +5357,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:9" ht="15.75" customHeight="1">
       <c r="A118" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>76</v>
@@ -5225,9 +5386,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:9" ht="15.75" customHeight="1">
       <c r="A119" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>76</v>
@@ -5254,9 +5415,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:9" ht="15.75" customHeight="1">
       <c r="A120" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>76</v>
@@ -5283,9 +5444,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:9" ht="15.75" customHeight="1">
       <c r="A121" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>76</v>
@@ -5312,9 +5473,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:9" ht="15.75" customHeight="1">
       <c r="A122" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>76</v>
@@ -5341,9 +5502,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:9" ht="15.75" customHeight="1">
       <c r="A123" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>76</v>
@@ -5370,9 +5531,9 @@
         <v>356</v>
       </c>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:9" ht="15.75" customHeight="1">
       <c r="A124" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>76</v>
@@ -5399,9 +5560,9 @@
         <v>361</v>
       </c>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:9" ht="15.75" customHeight="1">
       <c r="A125" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>76</v>
@@ -5428,9 +5589,9 @@
         <v>361</v>
       </c>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:9" ht="15.75" customHeight="1">
       <c r="A126" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>76</v>
@@ -5457,9 +5618,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:9" ht="15.75" customHeight="1">
       <c r="A127" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>76</v>
@@ -5486,9 +5647,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:9" ht="15.75" customHeight="1">
       <c r="A128" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>76</v>
@@ -5515,9 +5676,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:9" ht="15.75" customHeight="1">
       <c r="A129" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>76</v>
@@ -5544,9 +5705,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:9" ht="15.75" customHeight="1">
       <c r="A130" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>76</v>
@@ -5573,9 +5734,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:9" ht="15.75" customHeight="1">
       <c r="A131" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>91</v>
@@ -5602,9 +5763,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:9" ht="15.75" customHeight="1">
       <c r="A132" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>91</v>
@@ -5631,9 +5792,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:9" ht="15.75" customHeight="1">
       <c r="A133" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>91</v>
@@ -5660,9 +5821,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:9" ht="15.75" customHeight="1">
       <c r="A134" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>91</v>
@@ -5689,9 +5850,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:9" ht="15.75" customHeight="1">
       <c r="A135" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>91</v>
@@ -5718,9 +5879,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:9" ht="15.75" customHeight="1">
       <c r="A136" s="2">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>91</v>
@@ -5747,9 +5908,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:9" ht="15.75" customHeight="1">
       <c r="A137" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>136</v>
@@ -5776,9 +5937,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:9" ht="15.75" customHeight="1">
       <c r="A138" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B138" s="14" t="s">
         <v>76</v>
@@ -5805,9 +5966,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:9" ht="15.75" customHeight="1">
       <c r="A139" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B139" s="14" t="s">
         <v>91</v>
@@ -5834,9 +5995,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:9" ht="15.75" customHeight="1">
       <c r="A140" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B140" s="14" t="s">
         <v>91</v>
@@ -5863,9 +6024,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:9" ht="15.75" customHeight="1">
       <c r="A141" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B141" s="14" t="s">
         <v>91</v>
@@ -5892,9 +6053,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:9" ht="15.75" customHeight="1">
       <c r="A142" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B142" s="14" t="s">
         <v>91</v>
@@ -5921,9 +6082,9 @@
         <v>404</v>
       </c>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:9" ht="15.75" customHeight="1">
       <c r="A143" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B143" s="14" t="s">
         <v>91</v>
@@ -5950,9 +6111,9 @@
         <v>407</v>
       </c>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:9" ht="15.75" customHeight="1">
       <c r="A144" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B144" s="14" t="s">
         <v>91</v>
@@ -5979,9 +6140,9 @@
         <v>412</v>
       </c>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:9" ht="15.75" customHeight="1">
       <c r="A145" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B145" s="14" t="s">
         <v>136</v>
@@ -6008,9 +6169,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:9" ht="15.75" customHeight="1">
       <c r="A146" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B146" s="14" t="s">
         <v>91</v>
@@ -6037,9 +6198,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:9" ht="15.75" customHeight="1">
       <c r="A147" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B147" s="14" t="s">
         <v>91</v>
@@ -6066,9 +6227,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:9" ht="15.75" customHeight="1">
       <c r="A148" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B148" s="14" t="s">
         <v>104</v>
@@ -6095,9 +6256,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:9" ht="15.75" customHeight="1">
       <c r="A149" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B149" s="14" t="s">
         <v>104</v>
@@ -6124,9 +6285,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:9" ht="15.75" customHeight="1">
       <c r="A150" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B150" s="14" t="s">
         <v>104</v>
@@ -6153,9 +6314,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:9" ht="15.75" customHeight="1">
       <c r="A151" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B151" s="14" t="s">
         <v>104</v>
@@ -6182,9 +6343,9 @@
         <v>427</v>
       </c>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:9" ht="15.75" customHeight="1">
       <c r="A152" s="14">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="B152" s="14" t="s">
         <v>104</v>
@@ -6211,2589 +6372,2902 @@
         <v>427</v>
       </c>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="G153" s="16"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="G154" s="16"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="G155" s="16"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="G156" s="16"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="G157" s="16"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="G158" s="16"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="G159" s="16"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="G160" s="16"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="G161" s="16"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="G162" s="16"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="G163" s="16"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="G164" s="16"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="153" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A153">
+        <v>2026</v>
+      </c>
+      <c r="B153" t="s">
+        <v>104</v>
+      </c>
+      <c r="C153" t="s">
+        <v>416</v>
+      </c>
+      <c r="D153" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" t="s">
+        <v>430</v>
+      </c>
+      <c r="F153" t="s">
+        <v>13</v>
+      </c>
+      <c r="G153" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H153" t="s">
+        <v>431</v>
+      </c>
+      <c r="I153" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A154">
+        <v>2026</v>
+      </c>
+      <c r="B154" t="s">
+        <v>104</v>
+      </c>
+      <c r="C154" t="s">
+        <v>433</v>
+      </c>
+      <c r="D154" t="s">
+        <v>96</v>
+      </c>
+      <c r="E154" t="s">
+        <v>434</v>
+      </c>
+      <c r="F154" t="s">
+        <v>19</v>
+      </c>
+      <c r="G154" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H154" t="s">
+        <v>435</v>
+      </c>
+      <c r="I154" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A155">
+        <v>2026</v>
+      </c>
+      <c r="B155" t="s">
+        <v>104</v>
+      </c>
+      <c r="C155" t="s">
+        <v>419</v>
+      </c>
+      <c r="D155" t="s">
+        <v>33</v>
+      </c>
+      <c r="E155" t="s">
+        <v>420</v>
+      </c>
+      <c r="F155" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H155" t="s">
+        <v>436</v>
+      </c>
+      <c r="I155" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A156">
+        <v>2026</v>
+      </c>
+      <c r="B156" t="s">
+        <v>104</v>
+      </c>
+      <c r="C156" t="s">
+        <v>438</v>
+      </c>
+      <c r="D156" t="s">
+        <v>398</v>
+      </c>
+      <c r="E156" t="s">
+        <v>439</v>
+      </c>
+      <c r="F156" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H156" t="s">
+        <v>14</v>
+      </c>
+      <c r="I156" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A157">
+        <v>2026</v>
+      </c>
+      <c r="B157" t="s">
+        <v>136</v>
+      </c>
+      <c r="C157" t="s">
+        <v>138</v>
+      </c>
+      <c r="D157" t="s">
+        <v>391</v>
+      </c>
+      <c r="E157" t="s">
+        <v>441</v>
+      </c>
+      <c r="F157" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H157" t="s">
+        <v>167</v>
+      </c>
+      <c r="I157" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A158">
+        <v>2026</v>
+      </c>
+      <c r="B158" t="s">
+        <v>91</v>
+      </c>
+      <c r="C158" t="s">
+        <v>382</v>
+      </c>
+      <c r="D158" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" t="s">
+        <v>396</v>
+      </c>
+      <c r="F158" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H158" t="s">
+        <v>397</v>
+      </c>
+      <c r="I158" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A159">
+        <v>2026</v>
+      </c>
+      <c r="B159" t="s">
+        <v>104</v>
+      </c>
+      <c r="C159" t="s">
+        <v>438</v>
+      </c>
+      <c r="D159" t="s">
+        <v>33</v>
+      </c>
+      <c r="E159" t="s">
+        <v>443</v>
+      </c>
+      <c r="F159" t="s">
+        <v>119</v>
+      </c>
+      <c r="G159" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H159" t="s">
+        <v>14</v>
+      </c>
+      <c r="I159" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A160">
+        <v>2026</v>
+      </c>
+      <c r="B160" t="s">
+        <v>123</v>
+      </c>
+      <c r="C160" t="s">
+        <v>444</v>
+      </c>
+      <c r="D160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" t="s">
+        <v>445</v>
+      </c>
+      <c r="F160" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H160" t="s">
+        <v>446</v>
+      </c>
+      <c r="I160" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A161">
+        <v>2026</v>
+      </c>
+      <c r="B161" t="s">
+        <v>123</v>
+      </c>
+      <c r="C161" t="s">
+        <v>447</v>
+      </c>
+      <c r="D161" t="s">
+        <v>96</v>
+      </c>
+      <c r="E161" t="s">
+        <v>448</v>
+      </c>
+      <c r="F161" t="s">
+        <v>449</v>
+      </c>
+      <c r="G161" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H161" t="s">
+        <v>450</v>
+      </c>
+      <c r="I161" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A162">
+        <v>2026</v>
+      </c>
+      <c r="B162" t="s">
+        <v>123</v>
+      </c>
+      <c r="C162" t="s">
+        <v>451</v>
+      </c>
+      <c r="D162" t="s">
+        <v>96</v>
+      </c>
+      <c r="E162" t="s">
+        <v>452</v>
+      </c>
+      <c r="F162" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H162" t="s">
+        <v>14</v>
+      </c>
+      <c r="I162" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A163">
+        <v>2026</v>
+      </c>
+      <c r="B163" t="s">
+        <v>123</v>
+      </c>
+      <c r="C163" t="s">
+        <v>444</v>
+      </c>
+      <c r="D163" t="s">
+        <v>398</v>
+      </c>
+      <c r="E163" t="s">
+        <v>453</v>
+      </c>
+      <c r="F163" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H163" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A164">
+        <v>2026</v>
+      </c>
+      <c r="B164" t="s">
+        <v>123</v>
+      </c>
+      <c r="C164" t="s">
+        <v>454</v>
+      </c>
+      <c r="D164" t="s">
+        <v>455</v>
+      </c>
+      <c r="E164" t="s">
+        <v>456</v>
+      </c>
+      <c r="F164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H164" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15.75" customHeight="1">
       <c r="G165" s="16"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:9" ht="15.75" customHeight="1">
       <c r="G166" s="16"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:9" ht="15.75" customHeight="1">
       <c r="G167" s="16"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:9" ht="15.75" customHeight="1">
       <c r="G168" s="16"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:9" ht="15.75" customHeight="1">
       <c r="G169" s="16"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:9" ht="15.75" customHeight="1">
       <c r="G170" s="16"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:9" ht="15.75" customHeight="1">
       <c r="G171" s="16"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:9" ht="15.75" customHeight="1">
       <c r="G172" s="16"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:9" ht="15.75" customHeight="1">
       <c r="G173" s="16"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:9" ht="15.75" customHeight="1">
       <c r="G174" s="16"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:9" ht="15.75" customHeight="1">
       <c r="G175" s="16"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:9" ht="15.75" customHeight="1">
       <c r="G176" s="16"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="7:7" ht="15.75" customHeight="1">
       <c r="G177" s="16"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="7:7" ht="15.75" customHeight="1">
       <c r="G178" s="16"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="7:7" ht="15.75" customHeight="1">
       <c r="G179" s="16"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="7:7" ht="15.75" customHeight="1">
       <c r="G180" s="16"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="7:7" ht="15.75" customHeight="1">
       <c r="G181" s="16"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="7:7" ht="15.75" customHeight="1">
       <c r="G182" s="16"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="7:7" ht="15.75" customHeight="1">
       <c r="G183" s="16"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="7:7" ht="15.75" customHeight="1">
       <c r="G184" s="16"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="7:7" ht="15.75" customHeight="1">
       <c r="G185" s="16"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="7:7" ht="15.75" customHeight="1">
       <c r="G186" s="16"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="7:7" ht="15.75" customHeight="1">
       <c r="G187" s="16"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="7:7" ht="15.75" customHeight="1">
       <c r="G188" s="16"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="7:7" ht="15.75" customHeight="1">
       <c r="G189" s="16"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="7:7" ht="15.75" customHeight="1">
       <c r="G190" s="16"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="7:7" ht="15.75" customHeight="1">
       <c r="G191" s="16"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="7:7" ht="15.75" customHeight="1">
       <c r="G192" s="16"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="7:7" ht="15.75" customHeight="1">
       <c r="G193" s="16"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="7:7" ht="15.75" customHeight="1">
       <c r="G194" s="16"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="7:7" ht="15.75" customHeight="1">
       <c r="G195" s="16"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="7:7" ht="15.75" customHeight="1">
       <c r="G196" s="16"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="7:7" ht="15.75" customHeight="1">
       <c r="G197" s="16"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="7:7" ht="15.75" customHeight="1">
       <c r="G198" s="16"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="7:7" ht="15.75" customHeight="1">
       <c r="G199" s="16"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="7:7" ht="15.75" customHeight="1">
       <c r="G200" s="16"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="7:7" ht="15.75" customHeight="1">
       <c r="G201" s="16"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="7:7" ht="15.75" customHeight="1">
       <c r="G202" s="16"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="7:7" ht="15.75" customHeight="1">
       <c r="G203" s="16"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="7:7" ht="15.75" customHeight="1">
       <c r="G204" s="16"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="7:7" ht="15.75" customHeight="1">
       <c r="G205" s="16"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="7:7" ht="15.75" customHeight="1">
       <c r="G206" s="16"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="7:7" ht="15.75" customHeight="1">
       <c r="G207" s="16"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="7:7" ht="15.75" customHeight="1">
       <c r="G208" s="16"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="7:7" ht="15.75" customHeight="1">
       <c r="G209" s="16"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="7:7" ht="15.75" customHeight="1">
       <c r="G210" s="16"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="7:7" ht="15.75" customHeight="1">
       <c r="G211" s="16"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="7:7" ht="15.75" customHeight="1">
       <c r="G212" s="16"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="7:7" ht="15.75" customHeight="1">
       <c r="G213" s="16"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="7:7" ht="15.75" customHeight="1">
       <c r="G214" s="16"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="7:7" ht="15.75" customHeight="1">
       <c r="G215" s="16"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="7:7" ht="15.75" customHeight="1">
       <c r="G216" s="16"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="7:7" ht="15.75" customHeight="1">
       <c r="G217" s="16"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="7:7" ht="15.75" customHeight="1">
       <c r="G218" s="16"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="7:7" ht="15.75" customHeight="1">
       <c r="G219" s="16"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="7:7" ht="15.75" customHeight="1">
       <c r="G220" s="16"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="7:7" ht="15.75" customHeight="1">
       <c r="G221" s="16"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="7:7" ht="15.75" customHeight="1">
       <c r="G222" s="16"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="7:7" ht="15.75" customHeight="1">
       <c r="G223" s="16"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="7:7" ht="15.75" customHeight="1">
       <c r="G224" s="16"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="7:7" ht="15.75" customHeight="1">
       <c r="G225" s="16"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="7:7" ht="15.75" customHeight="1">
       <c r="G226" s="16"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="7:7" ht="15.75" customHeight="1">
       <c r="G227" s="16"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="7:7" ht="15.75" customHeight="1">
       <c r="G228" s="16"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="7:7" ht="15.75" customHeight="1">
       <c r="G229" s="16"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="7:7" ht="15.75" customHeight="1">
       <c r="G230" s="16"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="7:7" ht="15.75" customHeight="1">
       <c r="G231" s="16"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="7:7" ht="15.75" customHeight="1">
       <c r="G232" s="16"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="7:7" ht="15.75" customHeight="1">
       <c r="G233" s="16"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="7:7" ht="15.75" customHeight="1">
       <c r="G234" s="16"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="7:7" ht="15.75" customHeight="1">
       <c r="G235" s="16"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="7:7" ht="15.75" customHeight="1">
       <c r="G236" s="16"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="7:7" ht="15.75" customHeight="1">
       <c r="G237" s="16"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="7:7" ht="15.75" customHeight="1">
       <c r="G238" s="16"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="7:7" ht="15.75" customHeight="1">
       <c r="G239" s="16"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="7:7" ht="15.75" customHeight="1">
       <c r="G240" s="16"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="7:7" ht="15.75" customHeight="1">
       <c r="G241" s="16"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="7:7" ht="15.75" customHeight="1">
       <c r="G242" s="16"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="7:7" ht="15.75" customHeight="1">
       <c r="G243" s="16"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="7:7" ht="15.75" customHeight="1">
       <c r="G244" s="16"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="7:7" ht="15.75" customHeight="1">
       <c r="G245" s="16"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="7:7" ht="15.75" customHeight="1">
       <c r="G246" s="16"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="7:7" ht="15.75" customHeight="1">
       <c r="G247" s="16"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="7:7" ht="15.75" customHeight="1">
       <c r="G248" s="16"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="7:7" ht="15.75" customHeight="1">
       <c r="G249" s="16"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="7:7" ht="15.75" customHeight="1">
       <c r="G250" s="16"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="7:7" ht="15.75" customHeight="1">
       <c r="G251" s="16"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="7:7" ht="15.75" customHeight="1">
       <c r="G252" s="16"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="7:7" ht="15.75" customHeight="1">
       <c r="G253" s="16"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="7:7" ht="15.75" customHeight="1">
       <c r="G254" s="16"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="7:7" ht="15.75" customHeight="1">
       <c r="G255" s="16"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="7:7" ht="15.75" customHeight="1">
       <c r="G256" s="16"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="7:7" ht="15.75" customHeight="1">
       <c r="G257" s="16"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="7:7" ht="15.75" customHeight="1">
       <c r="G258" s="16"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="7:7" ht="15.75" customHeight="1">
       <c r="G259" s="16"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="7:7" ht="15.75" customHeight="1">
       <c r="G260" s="16"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="7:7" ht="15.75" customHeight="1">
       <c r="G261" s="16"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="7:7" ht="15.75" customHeight="1">
       <c r="G262" s="16"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="7:7" ht="15.75" customHeight="1">
       <c r="G263" s="16"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="7:7" ht="15.75" customHeight="1">
       <c r="G264" s="16"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="7:7" ht="15.75" customHeight="1">
       <c r="G265" s="16"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="7:7" ht="15.75" customHeight="1">
       <c r="G266" s="16"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="7:7" ht="15.75" customHeight="1">
       <c r="G267" s="16"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="7:7" ht="15.75" customHeight="1">
       <c r="G268" s="16"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="7:7" ht="15.75" customHeight="1">
       <c r="G269" s="16"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="7:7" ht="15.75" customHeight="1">
       <c r="G270" s="16"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="7:7" ht="15.75" customHeight="1">
       <c r="G271" s="16"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="7:7" ht="15.75" customHeight="1">
       <c r="G272" s="16"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="7:7" ht="15.75" customHeight="1">
       <c r="G273" s="16"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="7:7" ht="15.75" customHeight="1">
       <c r="G274" s="16"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="7:7" ht="15.75" customHeight="1">
       <c r="G275" s="16"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="7:7" ht="15.75" customHeight="1">
       <c r="G276" s="16"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="7:7" ht="15.75" customHeight="1">
       <c r="G277" s="16"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="7:7" ht="15.75" customHeight="1">
       <c r="G278" s="16"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="7:7" ht="15.75" customHeight="1">
       <c r="G279" s="16"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="7:7" ht="15.75" customHeight="1">
       <c r="G280" s="16"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="7:7" ht="15.75" customHeight="1">
       <c r="G281" s="16"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="7:7" ht="15.75" customHeight="1">
       <c r="G282" s="16"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="7:7" ht="15.75" customHeight="1">
       <c r="G283" s="16"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="7:7" ht="15.75" customHeight="1">
       <c r="G284" s="16"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="7:7" ht="15.75" customHeight="1">
       <c r="G285" s="16"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="7:7" ht="15.75" customHeight="1">
       <c r="G286" s="16"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="7:7" ht="15.75" customHeight="1">
       <c r="G287" s="16"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="7:7" ht="15.75" customHeight="1">
       <c r="G288" s="16"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="7:7" ht="15.75" customHeight="1">
       <c r="G289" s="16"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="7:7" ht="15.75" customHeight="1">
       <c r="G290" s="16"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="7:7" ht="15.75" customHeight="1">
       <c r="G291" s="16"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="7:7" ht="15.75" customHeight="1">
       <c r="G292" s="16"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="7:7" ht="15.75" customHeight="1">
       <c r="G293" s="16"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="7:7" ht="15.75" customHeight="1">
       <c r="G294" s="16"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="7:7" ht="15.75" customHeight="1">
       <c r="G295" s="16"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="7:7" ht="15.75" customHeight="1">
       <c r="G296" s="16"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="7:7" ht="15.75" customHeight="1">
       <c r="G297" s="16"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="7:7" ht="15.75" customHeight="1">
       <c r="G298" s="16"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="7:7" ht="15.75" customHeight="1">
       <c r="G299" s="16"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="7:7" ht="15.75" customHeight="1">
       <c r="G300" s="16"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="7:7" ht="15.75" customHeight="1">
       <c r="G301" s="16"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="7:7" ht="15.75" customHeight="1">
       <c r="G302" s="16"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="7:7" ht="15.75" customHeight="1">
       <c r="G303" s="16"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="7:7" ht="15.75" customHeight="1">
       <c r="G304" s="16"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="7:7" ht="15.75" customHeight="1">
       <c r="G305" s="16"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="7:7" ht="15.75" customHeight="1">
       <c r="G306" s="16"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="7:7" ht="15.75" customHeight="1">
       <c r="G307" s="16"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="7:7" ht="15.75" customHeight="1">
       <c r="G308" s="16"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="7:7" ht="15.75" customHeight="1">
       <c r="G309" s="16"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="7:7" ht="15.75" customHeight="1">
       <c r="G310" s="16"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="7:7" ht="15.75" customHeight="1">
       <c r="G311" s="16"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="7:7" ht="15.75" customHeight="1">
       <c r="G312" s="16"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="7:7" ht="15.75" customHeight="1">
       <c r="G313" s="16"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="7:7" ht="15.75" customHeight="1">
       <c r="G314" s="16"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="7:7" ht="15.75" customHeight="1">
       <c r="G315" s="16"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="7:7" ht="15.75" customHeight="1">
       <c r="G316" s="16"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="7:7" ht="15.75" customHeight="1">
       <c r="G317" s="16"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="7:7" ht="15.75" customHeight="1">
       <c r="G318" s="16"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="7:7" ht="15.75" customHeight="1">
       <c r="G319" s="16"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="7:7" ht="15.75" customHeight="1">
       <c r="G320" s="16"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="7:7" ht="15.75" customHeight="1">
       <c r="G321" s="16"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="7:7" ht="15.75" customHeight="1">
       <c r="G322" s="16"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="7:7" ht="15.75" customHeight="1">
       <c r="G323" s="16"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="7:7" ht="15.75" customHeight="1">
       <c r="G324" s="16"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="7:7" ht="15.75" customHeight="1">
       <c r="G325" s="16"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="7:7" ht="15.75" customHeight="1">
       <c r="G326" s="16"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="7:7" ht="15.75" customHeight="1">
       <c r="G327" s="16"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="7:7" ht="15.75" customHeight="1">
       <c r="G328" s="16"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="7:7" ht="15.75" customHeight="1">
       <c r="G329" s="16"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="7:7" ht="15.75" customHeight="1">
       <c r="G330" s="16"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="7:7" ht="15.75" customHeight="1">
       <c r="G331" s="16"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="7:7" ht="15.75" customHeight="1">
       <c r="G332" s="16"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="7:7" ht="15.75" customHeight="1">
       <c r="G333" s="16"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="7:7" ht="15.75" customHeight="1">
       <c r="G334" s="16"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="7:7" ht="15.75" customHeight="1">
       <c r="G335" s="16"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="7:7" ht="15.75" customHeight="1">
       <c r="G336" s="16"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="7:7" ht="15.75" customHeight="1">
       <c r="G337" s="16"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="7:7" ht="15.75" customHeight="1">
       <c r="G338" s="16"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="7:7" ht="15.75" customHeight="1">
       <c r="G339" s="16"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="7:7" ht="15.75" customHeight="1">
       <c r="G340" s="16"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="7:7" ht="15.75" customHeight="1">
       <c r="G341" s="16"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="7:7" ht="15.75" customHeight="1">
       <c r="G342" s="16"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="7:7" ht="15.75" customHeight="1">
       <c r="G343" s="16"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="7:7" ht="15.75" customHeight="1">
       <c r="G344" s="16"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="7:7" ht="15.75" customHeight="1">
       <c r="G345" s="16"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="7:7" ht="15.75" customHeight="1">
       <c r="G346" s="16"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="7:7" ht="15.75" customHeight="1">
       <c r="G347" s="16"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="7:7" ht="15.75" customHeight="1">
       <c r="G348" s="16"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="7:7" ht="15.75" customHeight="1">
       <c r="G349" s="16"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="7:7" ht="15.75" customHeight="1">
       <c r="G350" s="16"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="7:7" ht="15.75" customHeight="1">
       <c r="G351" s="16"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="7:7" ht="15.75" customHeight="1">
       <c r="G352" s="16"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="7:7" ht="15.75" customHeight="1">
       <c r="G353" s="16"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="7:7" ht="15.75" customHeight="1">
       <c r="G354" s="16"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="7:7" ht="15.75" customHeight="1">
       <c r="G355" s="16"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="7:7" ht="15.75" customHeight="1">
       <c r="G356" s="16"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="7:7" ht="15.75" customHeight="1">
       <c r="G357" s="16"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="7:7" ht="15.75" customHeight="1">
       <c r="G358" s="16"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="7:7" ht="15.75" customHeight="1">
       <c r="G359" s="16"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="7:7" ht="15.75" customHeight="1">
       <c r="G360" s="16"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="7:7" ht="15.75" customHeight="1">
       <c r="G361" s="16"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="7:7" ht="15.75" customHeight="1">
       <c r="G362" s="16"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="7:7" ht="15.75" customHeight="1">
       <c r="G363" s="16"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="7:7" ht="15.75" customHeight="1">
       <c r="G364" s="16"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="7:7" ht="15.75" customHeight="1">
       <c r="G365" s="16"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="7:7" ht="15.75" customHeight="1">
       <c r="G366" s="16"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="7:7" ht="15.75" customHeight="1">
       <c r="G367" s="16"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="7:7" ht="15.75" customHeight="1">
       <c r="G368" s="16"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="7:7" ht="15.75" customHeight="1">
       <c r="G369" s="16"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="7:7" ht="15.75" customHeight="1">
       <c r="G370" s="16"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="7:7" ht="15.75" customHeight="1">
       <c r="G371" s="16"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="7:7" ht="15.75" customHeight="1">
       <c r="G372" s="16"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="7:7" ht="15.75" customHeight="1">
       <c r="G373" s="16"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="7:7" ht="15.75" customHeight="1">
       <c r="G374" s="16"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="7:7" ht="15.75" customHeight="1">
       <c r="G375" s="16"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="7:7" ht="15.75" customHeight="1">
       <c r="G376" s="16"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="7:7" ht="15.75" customHeight="1">
       <c r="G377" s="16"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="7:7" ht="15.75" customHeight="1">
       <c r="G378" s="16"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="7:7" ht="15.75" customHeight="1">
       <c r="G379" s="16"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="7:7" ht="15.75" customHeight="1">
       <c r="G380" s="16"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="7:7" ht="15.75" customHeight="1">
       <c r="G381" s="16"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="7:7" ht="15.75" customHeight="1">
       <c r="G382" s="16"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="7:7" ht="15.75" customHeight="1">
       <c r="G383" s="16"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="7:7" ht="15.75" customHeight="1">
       <c r="G384" s="16"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="7:7" ht="15.75" customHeight="1">
       <c r="G385" s="16"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="7:7" ht="15.75" customHeight="1">
       <c r="G386" s="16"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="7:7" ht="15.75" customHeight="1">
       <c r="G387" s="16"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="7:7" ht="15.75" customHeight="1">
       <c r="G388" s="16"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="7:7" ht="15.75" customHeight="1">
       <c r="G389" s="16"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="7:7" ht="15.75" customHeight="1">
       <c r="G390" s="16"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="7:7" ht="15.75" customHeight="1">
       <c r="G391" s="16"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="7:7" ht="15.75" customHeight="1">
       <c r="G392" s="16"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="7:7" ht="15.75" customHeight="1">
       <c r="G393" s="16"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="7:7" ht="15.75" customHeight="1">
       <c r="G394" s="16"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="7:7" ht="15.75" customHeight="1">
       <c r="G395" s="16"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="7:7" ht="15.75" customHeight="1">
       <c r="G396" s="16"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="7:7" ht="15.75" customHeight="1">
       <c r="G397" s="16"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="7:7" ht="15.75" customHeight="1">
       <c r="G398" s="16"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="7:7" ht="15.75" customHeight="1">
       <c r="G399" s="16"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="7:7" ht="15.75" customHeight="1">
       <c r="G400" s="16"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="7:7" ht="15.75" customHeight="1">
       <c r="G401" s="16"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="7:7" ht="15.75" customHeight="1">
       <c r="G402" s="16"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="7:7" ht="15.75" customHeight="1">
       <c r="G403" s="16"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="7:7" ht="15.75" customHeight="1">
       <c r="G404" s="16"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="7:7" ht="15.75" customHeight="1">
       <c r="G405" s="16"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="7:7" ht="15.75" customHeight="1">
       <c r="G406" s="16"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="7:7" ht="15.75" customHeight="1">
       <c r="G407" s="16"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="7:7" ht="15.75" customHeight="1">
       <c r="G408" s="16"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="7:7" ht="15.75" customHeight="1">
       <c r="G409" s="16"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="7:7" ht="15.75" customHeight="1">
       <c r="G410" s="16"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="7:7" ht="15.75" customHeight="1">
       <c r="G411" s="16"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="7:7" ht="15.75" customHeight="1">
       <c r="G412" s="16"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="7:7" ht="15.75" customHeight="1">
       <c r="G413" s="16"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="7:7" ht="15.75" customHeight="1">
       <c r="G414" s="16"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="7:7" ht="15.75" customHeight="1">
       <c r="G415" s="16"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="7:7" ht="15.75" customHeight="1">
       <c r="G416" s="16"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="7:7" ht="15.75" customHeight="1">
       <c r="G417" s="16"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="7:7" ht="15.75" customHeight="1">
       <c r="G418" s="16"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="7:7" ht="15.75" customHeight="1">
       <c r="G419" s="16"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="7:7" ht="15.75" customHeight="1">
       <c r="G420" s="16"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="7:7" ht="15.75" customHeight="1">
       <c r="G421" s="16"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="7:7" ht="15.75" customHeight="1">
       <c r="G422" s="16"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="7:7" ht="15.75" customHeight="1">
       <c r="G423" s="16"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="7:7" ht="15.75" customHeight="1">
       <c r="G424" s="16"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="7:7" ht="15.75" customHeight="1">
       <c r="G425" s="16"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="7:7" ht="15.75" customHeight="1">
       <c r="G426" s="16"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="7:7" ht="15.75" customHeight="1">
       <c r="G427" s="16"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="7:7" ht="15.75" customHeight="1">
       <c r="G428" s="16"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="7:7" ht="15.75" customHeight="1">
       <c r="G429" s="16"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="7:7" ht="15.75" customHeight="1">
       <c r="G430" s="16"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="7:7" ht="15.75" customHeight="1">
       <c r="G431" s="16"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="7:7" ht="15.75" customHeight="1">
       <c r="G432" s="16"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="7:7" ht="15.75" customHeight="1">
       <c r="G433" s="16"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="7:7" ht="15.75" customHeight="1">
       <c r="G434" s="16"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="7:7" ht="15.75" customHeight="1">
       <c r="G435" s="16"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="7:7" ht="15.75" customHeight="1">
       <c r="G436" s="16"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="7:7" ht="15.75" customHeight="1">
       <c r="G437" s="16"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="7:7" ht="15.75" customHeight="1">
       <c r="G438" s="16"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="7:7" ht="15.75" customHeight="1">
       <c r="G439" s="16"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="7:7" ht="15.75" customHeight="1">
       <c r="G440" s="16"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="7:7" ht="15.75" customHeight="1">
       <c r="G441" s="16"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="7:7" ht="15.75" customHeight="1">
       <c r="G442" s="16"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="7:7" ht="15.75" customHeight="1">
       <c r="G443" s="16"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="7:7" ht="15.75" customHeight="1">
       <c r="G444" s="16"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="7:7" ht="15.75" customHeight="1">
       <c r="G445" s="16"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="7:7" ht="15.75" customHeight="1">
       <c r="G446" s="16"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="7:7" ht="15.75" customHeight="1">
       <c r="G447" s="16"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="7:7" ht="15.75" customHeight="1">
       <c r="G448" s="16"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="7:7" ht="15.75" customHeight="1">
       <c r="G449" s="16"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="7:7" ht="15.75" customHeight="1">
       <c r="G450" s="16"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="7:7" ht="15.75" customHeight="1">
       <c r="G451" s="16"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="7:7" ht="15.75" customHeight="1">
       <c r="G452" s="16"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="7:7" ht="15.75" customHeight="1">
       <c r="G453" s="16"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="7:7" ht="15.75" customHeight="1">
       <c r="G454" s="16"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="7:7" ht="15.75" customHeight="1">
       <c r="G455" s="16"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="7:7" ht="15.75" customHeight="1">
       <c r="G456" s="16"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="7:7" ht="15.75" customHeight="1">
       <c r="G457" s="16"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="7:7" ht="15.75" customHeight="1">
       <c r="G458" s="16"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="7:7" ht="15.75" customHeight="1">
       <c r="G459" s="16"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="7:7" ht="15.75" customHeight="1">
       <c r="G460" s="16"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="7:7" ht="15.75" customHeight="1">
       <c r="G461" s="16"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="7:7" ht="15.75" customHeight="1">
       <c r="G462" s="16"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="7:7" ht="15.75" customHeight="1">
       <c r="G463" s="16"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="7:7" ht="15.75" customHeight="1">
       <c r="G464" s="16"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="7:7" ht="15.75" customHeight="1">
       <c r="G465" s="16"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="7:7" ht="15.75" customHeight="1">
       <c r="G466" s="16"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="7:7" ht="15.75" customHeight="1">
       <c r="G467" s="16"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="7:7" ht="15.75" customHeight="1">
       <c r="G468" s="16"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="7:7" ht="15.75" customHeight="1">
       <c r="G469" s="16"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="7:7" ht="15.75" customHeight="1">
       <c r="G470" s="16"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="7:7" ht="15.75" customHeight="1">
       <c r="G471" s="16"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="7:7" ht="15.75" customHeight="1">
       <c r="G472" s="16"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="7:7" ht="15.75" customHeight="1">
       <c r="G473" s="16"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="7:7" ht="15.75" customHeight="1">
       <c r="G474" s="16"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="7:7" ht="15.75" customHeight="1">
       <c r="G475" s="16"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="7:7" ht="15.75" customHeight="1">
       <c r="G476" s="16"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="7:7" ht="15.75" customHeight="1">
       <c r="G477" s="16"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="7:7" ht="15.75" customHeight="1">
       <c r="G478" s="16"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="7:7" ht="15.75" customHeight="1">
       <c r="G479" s="16"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="7:7" ht="15.75" customHeight="1">
       <c r="G480" s="16"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="7:7" ht="15.75" customHeight="1">
       <c r="G481" s="16"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="7:7" ht="15.75" customHeight="1">
       <c r="G482" s="16"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="7:7" ht="15.75" customHeight="1">
       <c r="G483" s="16"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="7:7" ht="15.75" customHeight="1">
       <c r="G484" s="16"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="7:7" ht="15.75" customHeight="1">
       <c r="G485" s="16"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="7:7" ht="15.75" customHeight="1">
       <c r="G486" s="16"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="7:7" ht="15.75" customHeight="1">
       <c r="G487" s="16"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="7:7" ht="15.75" customHeight="1">
       <c r="G488" s="16"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="7:7" ht="15.75" customHeight="1">
       <c r="G489" s="16"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="7:7" ht="15.75" customHeight="1">
       <c r="G490" s="16"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="7:7" ht="15.75" customHeight="1">
       <c r="G491" s="16"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="7:7" ht="15.75" customHeight="1">
       <c r="G492" s="16"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="7:7" ht="15.75" customHeight="1">
       <c r="G493" s="16"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="7:7" ht="15.75" customHeight="1">
       <c r="G494" s="16"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="7:7" ht="15.75" customHeight="1">
       <c r="G495" s="16"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="7:7" ht="15.75" customHeight="1">
       <c r="G496" s="16"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="7:7" ht="15.75" customHeight="1">
       <c r="G497" s="16"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="7:7" ht="15.75" customHeight="1">
       <c r="G498" s="16"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="7:7" ht="15.75" customHeight="1">
       <c r="G499" s="16"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="7:7" ht="15.75" customHeight="1">
       <c r="G500" s="16"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="7:7" ht="15.75" customHeight="1">
       <c r="G501" s="16"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="7:7" ht="15.75" customHeight="1">
       <c r="G502" s="16"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="7:7" ht="15.75" customHeight="1">
       <c r="G503" s="16"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="7:7" ht="15.75" customHeight="1">
       <c r="G504" s="16"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="7:7" ht="15.75" customHeight="1">
       <c r="G505" s="16"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="7:7" ht="15.75" customHeight="1">
       <c r="G506" s="16"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="7:7" ht="15.75" customHeight="1">
       <c r="G507" s="16"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="7:7" ht="15.75" customHeight="1">
       <c r="G508" s="16"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="7:7" ht="15.75" customHeight="1">
       <c r="G509" s="16"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="7:7" ht="15.75" customHeight="1">
       <c r="G510" s="16"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="7:7" ht="15.75" customHeight="1">
       <c r="G511" s="16"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="7:7" ht="15.75" customHeight="1">
       <c r="G512" s="16"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="7:7" ht="15.75" customHeight="1">
       <c r="G513" s="16"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="7:7" ht="15.75" customHeight="1">
       <c r="G514" s="16"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="7:7" ht="15.75" customHeight="1">
       <c r="G515" s="16"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="7:7" ht="15.75" customHeight="1">
       <c r="G516" s="16"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="7:7" ht="15.75" customHeight="1">
       <c r="G517" s="16"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="7:7" ht="15.75" customHeight="1">
       <c r="G518" s="16"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="7:7" ht="15.75" customHeight="1">
       <c r="G519" s="16"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="7:7" ht="15.75" customHeight="1">
       <c r="G520" s="16"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="7:7" ht="15.75" customHeight="1">
       <c r="G521" s="16"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="7:7" ht="15.75" customHeight="1">
       <c r="G522" s="16"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="7:7" ht="15.75" customHeight="1">
       <c r="G523" s="16"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="7:7" ht="15.75" customHeight="1">
       <c r="G524" s="16"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="7:7" ht="15.75" customHeight="1">
       <c r="G525" s="16"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="7:7" ht="15.75" customHeight="1">
       <c r="G526" s="16"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="7:7" ht="15.75" customHeight="1">
       <c r="G527" s="16"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="7:7" ht="15.75" customHeight="1">
       <c r="G528" s="16"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="7:7" ht="15.75" customHeight="1">
       <c r="G529" s="16"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="7:7" ht="15.75" customHeight="1">
       <c r="G530" s="16"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="7:7" ht="15.75" customHeight="1">
       <c r="G531" s="16"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="7:7" ht="15.75" customHeight="1">
       <c r="G532" s="16"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="7:7" ht="15.75" customHeight="1">
       <c r="G533" s="16"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="7:7" ht="15.75" customHeight="1">
       <c r="G534" s="16"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="7:7" ht="15.75" customHeight="1">
       <c r="G535" s="16"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="7:7" ht="15.75" customHeight="1">
       <c r="G536" s="16"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="7:7" ht="15.75" customHeight="1">
       <c r="G537" s="16"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="7:7" ht="15.75" customHeight="1">
       <c r="G538" s="16"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="7:7" ht="15.75" customHeight="1">
       <c r="G539" s="16"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="7:7" ht="15.75" customHeight="1">
       <c r="G540" s="16"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="7:7" ht="15.75" customHeight="1">
       <c r="G541" s="16"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="7:7" ht="15.75" customHeight="1">
       <c r="G542" s="16"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="7:7" ht="15.75" customHeight="1">
       <c r="G543" s="16"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="7:7" ht="15.75" customHeight="1">
       <c r="G544" s="16"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="7:7" ht="15.75" customHeight="1">
       <c r="G545" s="16"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="7:7" ht="15.75" customHeight="1">
       <c r="G546" s="16"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="7:7" ht="15.75" customHeight="1">
       <c r="G547" s="16"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="7:7" ht="15.75" customHeight="1">
       <c r="G548" s="16"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="7:7" ht="15.75" customHeight="1">
       <c r="G549" s="16"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="7:7" ht="15.75" customHeight="1">
       <c r="G550" s="16"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="7:7" ht="15.75" customHeight="1">
       <c r="G551" s="16"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="7:7" ht="15.75" customHeight="1">
       <c r="G552" s="16"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="7:7" ht="15.75" customHeight="1">
       <c r="G553" s="16"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="7:7" ht="15.75" customHeight="1">
       <c r="G554" s="16"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="7:7" ht="15.75" customHeight="1">
       <c r="G555" s="16"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="7:7" ht="15.75" customHeight="1">
       <c r="G556" s="16"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="7:7" ht="15.75" customHeight="1">
       <c r="G557" s="16"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="7:7" ht="15.75" customHeight="1">
       <c r="G558" s="16"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="7:7" ht="15.75" customHeight="1">
       <c r="G559" s="16"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="7:7" ht="15.75" customHeight="1">
       <c r="G560" s="16"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="7:7" ht="15.75" customHeight="1">
       <c r="G561" s="16"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="7:7" ht="15.75" customHeight="1">
       <c r="G562" s="16"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="7:7" ht="15.75" customHeight="1">
       <c r="G563" s="16"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="7:7" ht="15.75" customHeight="1">
       <c r="G564" s="16"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="7:7" ht="15.75" customHeight="1">
       <c r="G565" s="16"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="7:7" ht="15.75" customHeight="1">
       <c r="G566" s="16"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="7:7" ht="15.75" customHeight="1">
       <c r="G567" s="16"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="7:7" ht="15.75" customHeight="1">
       <c r="G568" s="16"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="7:7" ht="15.75" customHeight="1">
       <c r="G569" s="16"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="7:7" ht="15.75" customHeight="1">
       <c r="G570" s="16"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="7:7" ht="15.75" customHeight="1">
       <c r="G571" s="16"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="7:7" ht="15.75" customHeight="1">
       <c r="G572" s="16"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="7:7" ht="15.75" customHeight="1">
       <c r="G573" s="16"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="7:7" ht="15.75" customHeight="1">
       <c r="G574" s="16"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="7:7" ht="15.75" customHeight="1">
       <c r="G575" s="16"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="7:7" ht="15.75" customHeight="1">
       <c r="G576" s="16"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="7:7" ht="15.75" customHeight="1">
       <c r="G577" s="16"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="7:7" ht="15.75" customHeight="1">
       <c r="G578" s="16"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="7:7" ht="15.75" customHeight="1">
       <c r="G579" s="16"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="7:7" ht="15.75" customHeight="1">
       <c r="G580" s="16"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="7:7" ht="15.75" customHeight="1">
       <c r="G581" s="16"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="7:7" ht="15.75" customHeight="1">
       <c r="G582" s="16"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="7:7" ht="15.75" customHeight="1">
       <c r="G583" s="16"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="7:7" ht="15.75" customHeight="1">
       <c r="G584" s="16"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="7:7" ht="15.75" customHeight="1">
       <c r="G585" s="16"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="7:7" ht="15.75" customHeight="1">
       <c r="G586" s="16"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="7:7" ht="15.75" customHeight="1">
       <c r="G587" s="16"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="7:7" ht="15.75" customHeight="1">
       <c r="G588" s="16"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="7:7" ht="15.75" customHeight="1">
       <c r="G589" s="16"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="7:7" ht="15.75" customHeight="1">
       <c r="G590" s="16"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="7:7" ht="15.75" customHeight="1">
       <c r="G591" s="16"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="7:7" ht="15.75" customHeight="1">
       <c r="G592" s="16"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="7:7" ht="15.75" customHeight="1">
       <c r="G593" s="16"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="7:7" ht="15.75" customHeight="1">
       <c r="G594" s="16"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="7:7" ht="15.75" customHeight="1">
       <c r="G595" s="16"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="7:7" ht="15.75" customHeight="1">
       <c r="G596" s="16"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="7:7" ht="15.75" customHeight="1">
       <c r="G597" s="16"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="7:7" ht="15.75" customHeight="1">
       <c r="G598" s="16"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="7:7" ht="15.75" customHeight="1">
       <c r="G599" s="16"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="7:7" ht="15.75" customHeight="1">
       <c r="G600" s="16"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="7:7" ht="15.75" customHeight="1">
       <c r="G601" s="16"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="7:7" ht="15.75" customHeight="1">
       <c r="G602" s="16"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="7:7" ht="15.75" customHeight="1">
       <c r="G603" s="16"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="7:7" ht="15.75" customHeight="1">
       <c r="G604" s="16"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="7:7" ht="15.75" customHeight="1">
       <c r="G605" s="16"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="7:7" ht="15.75" customHeight="1">
       <c r="G606" s="16"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="7:7" ht="15.75" customHeight="1">
       <c r="G607" s="16"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="7:7" ht="15.75" customHeight="1">
       <c r="G608" s="16"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="7:7" ht="15.75" customHeight="1">
       <c r="G609" s="16"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="7:7" ht="15.75" customHeight="1">
       <c r="G610" s="16"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="7:7" ht="15.75" customHeight="1">
       <c r="G611" s="16"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="7:7" ht="15.75" customHeight="1">
       <c r="G612" s="16"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="7:7" ht="15.75" customHeight="1">
       <c r="G613" s="16"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="7:7" ht="15.75" customHeight="1">
       <c r="G614" s="16"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="7:7" ht="15.75" customHeight="1">
       <c r="G615" s="16"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="7:7" ht="15.75" customHeight="1">
       <c r="G616" s="16"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="7:7" ht="15.75" customHeight="1">
       <c r="G617" s="16"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="7:7" ht="15.75" customHeight="1">
       <c r="G618" s="16"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="7:7" ht="15.75" customHeight="1">
       <c r="G619" s="16"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="7:7" ht="15.75" customHeight="1">
       <c r="G620" s="16"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="7:7" ht="15.75" customHeight="1">
       <c r="G621" s="16"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="7:7" ht="15.75" customHeight="1">
       <c r="G622" s="16"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="7:7" ht="15.75" customHeight="1">
       <c r="G623" s="16"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="7:7" ht="15.75" customHeight="1">
       <c r="G624" s="16"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="7:7" ht="15.75" customHeight="1">
       <c r="G625" s="16"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="7:7" ht="15.75" customHeight="1">
       <c r="G626" s="16"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="7:7" ht="15.75" customHeight="1">
       <c r="G627" s="16"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="7:7" ht="15.75" customHeight="1">
       <c r="G628" s="16"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="7:7" ht="15.75" customHeight="1">
       <c r="G629" s="16"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="7:7" ht="15.75" customHeight="1">
       <c r="G630" s="16"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="7:7" ht="15.75" customHeight="1">
       <c r="G631" s="16"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="7:7" ht="15.75" customHeight="1">
       <c r="G632" s="16"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="7:7" ht="15.75" customHeight="1">
       <c r="G633" s="16"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="7:7" ht="15.75" customHeight="1">
       <c r="G634" s="16"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="7:7" ht="15.75" customHeight="1">
       <c r="G635" s="16"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="7:7" ht="15.75" customHeight="1">
       <c r="G636" s="16"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="7:7" ht="15.75" customHeight="1">
       <c r="G637" s="16"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="7:7" ht="15.75" customHeight="1">
       <c r="G638" s="16"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="7:7" ht="15.75" customHeight="1">
       <c r="G639" s="16"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="7:7" ht="15.75" customHeight="1">
       <c r="G640" s="16"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="7:7" ht="15.75" customHeight="1">
       <c r="G641" s="16"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="7:7" ht="15.75" customHeight="1">
       <c r="G642" s="16"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="7:7" ht="15.75" customHeight="1">
       <c r="G643" s="16"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="7:7" ht="15.75" customHeight="1">
       <c r="G644" s="16"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="7:7" ht="15.75" customHeight="1">
       <c r="G645" s="16"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="7:7" ht="15.75" customHeight="1">
       <c r="G646" s="16"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="7:7" ht="15.75" customHeight="1">
       <c r="G647" s="16"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="7:7" ht="15.75" customHeight="1">
       <c r="G648" s="16"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="7:7" ht="15.75" customHeight="1">
       <c r="G649" s="16"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="7:7" ht="15.75" customHeight="1">
       <c r="G650" s="16"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="7:7" ht="15.75" customHeight="1">
       <c r="G651" s="16"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="7:7" ht="15.75" customHeight="1">
       <c r="G652" s="16"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="7:7" ht="15.75" customHeight="1">
       <c r="G653" s="16"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="7:7" ht="15.75" customHeight="1">
       <c r="G654" s="16"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="7:7" ht="15.75" customHeight="1">
       <c r="G655" s="16"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="7:7" ht="15.75" customHeight="1">
       <c r="G656" s="16"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="7:7" ht="15.75" customHeight="1">
       <c r="G657" s="16"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="7:7" ht="15.75" customHeight="1">
       <c r="G658" s="16"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="7:7" ht="15.75" customHeight="1">
       <c r="G659" s="16"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="7:7" ht="15.75" customHeight="1">
       <c r="G660" s="16"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="7:7" ht="15.75" customHeight="1">
       <c r="G661" s="16"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="7:7" ht="15.75" customHeight="1">
       <c r="G662" s="16"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="7:7" ht="15.75" customHeight="1">
       <c r="G663" s="16"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="7:7" ht="15.75" customHeight="1">
       <c r="G664" s="16"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="7:7" ht="15.75" customHeight="1">
       <c r="G665" s="16"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="7:7" ht="15.75" customHeight="1">
       <c r="G666" s="16"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="7:7" ht="15.75" customHeight="1">
       <c r="G667" s="16"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="7:7" ht="15.75" customHeight="1">
       <c r="G668" s="16"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="7:7" ht="15.75" customHeight="1">
       <c r="G669" s="16"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="7:7" ht="15.75" customHeight="1">
       <c r="G670" s="16"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="7:7" ht="15.75" customHeight="1">
       <c r="G671" s="16"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="7:7" ht="15.75" customHeight="1">
       <c r="G672" s="16"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="7:7" ht="15.75" customHeight="1">
       <c r="G673" s="16"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="7:7" ht="15.75" customHeight="1">
       <c r="G674" s="16"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="7:7" ht="15.75" customHeight="1">
       <c r="G675" s="16"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="7:7" ht="15.75" customHeight="1">
       <c r="G676" s="16"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="7:7" ht="15.75" customHeight="1">
       <c r="G677" s="16"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="7:7" ht="15.75" customHeight="1">
       <c r="G678" s="16"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="7:7" ht="15.75" customHeight="1">
       <c r="G679" s="16"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="7:7" ht="15.75" customHeight="1">
       <c r="G680" s="16"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="7:7" ht="15.75" customHeight="1">
       <c r="G681" s="16"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="7:7" ht="15.75" customHeight="1">
       <c r="G682" s="16"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="7:7" ht="15.75" customHeight="1">
       <c r="G683" s="16"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="7:7" ht="15.75" customHeight="1">
       <c r="G684" s="16"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="7:7" ht="15.75" customHeight="1">
       <c r="G685" s="16"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="7:7" ht="15.75" customHeight="1">
       <c r="G686" s="16"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="7:7" ht="15.75" customHeight="1">
       <c r="G687" s="16"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="7:7" ht="15.75" customHeight="1">
       <c r="G688" s="16"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="7:7" ht="15.75" customHeight="1">
       <c r="G689" s="16"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="7:7" ht="15.75" customHeight="1">
       <c r="G690" s="16"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="7:7" ht="15.75" customHeight="1">
       <c r="G691" s="16"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="7:7" ht="15.75" customHeight="1">
       <c r="G692" s="16"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="7:7" ht="15.75" customHeight="1">
       <c r="G693" s="16"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="7:7" ht="15.75" customHeight="1">
       <c r="G694" s="16"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="7:7" ht="15.75" customHeight="1">
       <c r="G695" s="16"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="7:7" ht="15.75" customHeight="1">
       <c r="G696" s="16"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="7:7" ht="15.75" customHeight="1">
       <c r="G697" s="16"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="7:7" ht="15.75" customHeight="1">
       <c r="G698" s="16"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="7:7" ht="15.75" customHeight="1">
       <c r="G699" s="16"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="7:7" ht="15.75" customHeight="1">
       <c r="G700" s="16"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="7:7" ht="15.75" customHeight="1">
       <c r="G701" s="16"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="7:7" ht="15.75" customHeight="1">
       <c r="G702" s="16"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="7:7" ht="15.75" customHeight="1">
       <c r="G703" s="16"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="7:7" ht="15.75" customHeight="1">
       <c r="G704" s="16"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="7:7" ht="15.75" customHeight="1">
       <c r="G705" s="16"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="7:7" ht="15.75" customHeight="1">
       <c r="G706" s="16"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="7:7" ht="15.75" customHeight="1">
       <c r="G707" s="16"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="7:7" ht="15.75" customHeight="1">
       <c r="G708" s="16"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="7:7" ht="15.75" customHeight="1">
       <c r="G709" s="16"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="7:7" ht="15.75" customHeight="1">
       <c r="G710" s="16"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="7:7" ht="15.75" customHeight="1">
       <c r="G711" s="16"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="7:7" ht="15.75" customHeight="1">
       <c r="G712" s="16"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="7:7" ht="15.75" customHeight="1">
       <c r="G713" s="16"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="7:7" ht="15.75" customHeight="1">
       <c r="G714" s="16"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="7:7" ht="15.75" customHeight="1">
       <c r="G715" s="16"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="7:7" ht="15.75" customHeight="1">
       <c r="G716" s="16"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="7:7" ht="15.75" customHeight="1">
       <c r="G717" s="16"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="7:7" ht="15.75" customHeight="1">
       <c r="G718" s="16"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="7:7" ht="15.75" customHeight="1">
       <c r="G719" s="16"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="7:7" ht="15.75" customHeight="1">
       <c r="G720" s="16"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="7:7" ht="15.75" customHeight="1">
       <c r="G721" s="16"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="7:7" ht="15.75" customHeight="1">
       <c r="G722" s="16"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="7:7" ht="15.75" customHeight="1">
       <c r="G723" s="16"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="7:7" ht="15.75" customHeight="1">
       <c r="G724" s="16"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="7:7" ht="15.75" customHeight="1">
       <c r="G725" s="16"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="7:7" ht="15.75" customHeight="1">
       <c r="G726" s="16"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="7:7" ht="15.75" customHeight="1">
       <c r="G727" s="16"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="7:7" ht="15.75" customHeight="1">
       <c r="G728" s="16"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="7:7" ht="15.75" customHeight="1">
       <c r="G729" s="16"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="7:7" ht="15.75" customHeight="1">
       <c r="G730" s="16"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="7:7" ht="15.75" customHeight="1">
       <c r="G731" s="16"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="7:7" ht="15.75" customHeight="1">
       <c r="G732" s="16"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="7:7" ht="15.75" customHeight="1">
       <c r="G733" s="16"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="7:7" ht="15.75" customHeight="1">
       <c r="G734" s="16"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="7:7" ht="15.75" customHeight="1">
       <c r="G735" s="16"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="7:7" ht="15.75" customHeight="1">
       <c r="G736" s="16"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="7:7" ht="15.75" customHeight="1">
       <c r="G737" s="16"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="7:7" ht="15.75" customHeight="1">
       <c r="G738" s="16"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="7:7" ht="15.75" customHeight="1">
       <c r="G739" s="16"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="7:7" ht="15.75" customHeight="1">
       <c r="G740" s="16"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="7:7" ht="15.75" customHeight="1">
       <c r="G741" s="16"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="7:7" ht="15.75" customHeight="1">
       <c r="G742" s="16"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="7:7" ht="15.75" customHeight="1">
       <c r="G743" s="16"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="7:7" ht="15.75" customHeight="1">
       <c r="G744" s="16"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="7:7" ht="15.75" customHeight="1">
       <c r="G745" s="16"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="7:7" ht="15.75" customHeight="1">
       <c r="G746" s="16"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="7:7" ht="15.75" customHeight="1">
       <c r="G747" s="16"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="7:7" ht="15.75" customHeight="1">
       <c r="G748" s="16"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="7:7" ht="15.75" customHeight="1">
       <c r="G749" s="16"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="7:7" ht="15.75" customHeight="1">
       <c r="G750" s="16"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="7:7" ht="15.75" customHeight="1">
       <c r="G751" s="16"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="7:7" ht="15.75" customHeight="1">
       <c r="G752" s="16"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="7:7" ht="15.75" customHeight="1">
       <c r="G753" s="16"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="7:7" ht="15.75" customHeight="1">
       <c r="G754" s="16"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="7:7" ht="15.75" customHeight="1">
       <c r="G755" s="16"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="7:7" ht="15.75" customHeight="1">
       <c r="G756" s="16"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="7:7" ht="15.75" customHeight="1">
       <c r="G757" s="16"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="7:7" ht="15.75" customHeight="1">
       <c r="G758" s="16"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="7:7" ht="15.75" customHeight="1">
       <c r="G759" s="16"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="7:7" ht="15.75" customHeight="1">
       <c r="G760" s="16"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="7:7" ht="15.75" customHeight="1">
       <c r="G761" s="16"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="7:7" ht="15.75" customHeight="1">
       <c r="G762" s="16"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="7:7" ht="15.75" customHeight="1">
       <c r="G763" s="16"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="7:7" ht="15.75" customHeight="1">
       <c r="G764" s="16"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="7:7" ht="15.75" customHeight="1">
       <c r="G765" s="16"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="7:7" ht="15.75" customHeight="1">
       <c r="G766" s="16"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="7:7" ht="15.75" customHeight="1">
       <c r="G767" s="16"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="7:7" ht="15.75" customHeight="1">
       <c r="G768" s="16"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="7:7" ht="15.75" customHeight="1">
       <c r="G769" s="16"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="7:7" ht="15.75" customHeight="1">
       <c r="G770" s="16"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="7:7" ht="15.75" customHeight="1">
       <c r="G771" s="16"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="7:7" ht="15.75" customHeight="1">
       <c r="G772" s="16"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="7:7" ht="15.75" customHeight="1">
       <c r="G773" s="16"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="7:7" ht="15.75" customHeight="1">
       <c r="G774" s="16"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="7:7" ht="15.75" customHeight="1">
       <c r="G775" s="16"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="7:7" ht="15.75" customHeight="1">
       <c r="G776" s="16"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="7:7" ht="15.75" customHeight="1">
       <c r="G777" s="16"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="7:7" ht="15.75" customHeight="1">
       <c r="G778" s="16"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="7:7" ht="15.75" customHeight="1">
       <c r="G779" s="16"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="7:7" ht="15.75" customHeight="1">
       <c r="G780" s="16"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="7:7" ht="15.75" customHeight="1">
       <c r="G781" s="16"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="7:7" ht="15.75" customHeight="1">
       <c r="G782" s="16"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="7:7" ht="15.75" customHeight="1">
       <c r="G783" s="16"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="7:7" ht="15.75" customHeight="1">
       <c r="G784" s="16"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="7:7" ht="15.75" customHeight="1">
       <c r="G785" s="16"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="7:7" ht="15.75" customHeight="1">
       <c r="G786" s="16"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="7:7" ht="15.75" customHeight="1">
       <c r="G787" s="16"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="7:7" ht="15.75" customHeight="1">
       <c r="G788" s="16"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="7:7" ht="15.75" customHeight="1">
       <c r="G789" s="16"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="7:7" ht="15.75" customHeight="1">
       <c r="G790" s="16"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="7:7" ht="15.75" customHeight="1">
       <c r="G791" s="16"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="7:7" ht="15.75" customHeight="1">
       <c r="G792" s="16"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="7:7" ht="15.75" customHeight="1">
       <c r="G793" s="16"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="7:7" ht="15.75" customHeight="1">
       <c r="G794" s="16"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="7:7" ht="15.75" customHeight="1">
       <c r="G795" s="16"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="7:7" ht="15.75" customHeight="1">
       <c r="G796" s="16"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="7:7" ht="15.75" customHeight="1">
       <c r="G797" s="16"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="7:7" ht="15.75" customHeight="1">
       <c r="G798" s="16"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="7:7" ht="15.75" customHeight="1">
       <c r="G799" s="16"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="7:7" ht="15.75" customHeight="1">
       <c r="G800" s="16"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="7:7" ht="15.75" customHeight="1">
       <c r="G801" s="16"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="7:7" ht="15.75" customHeight="1">
       <c r="G802" s="16"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="7:7" ht="15.75" customHeight="1">
       <c r="G803" s="16"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="7:7" ht="15.75" customHeight="1">
       <c r="G804" s="16"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="7:7" ht="15.75" customHeight="1">
       <c r="G805" s="16"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="7:7" ht="15.75" customHeight="1">
       <c r="G806" s="16"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="7:7" ht="15.75" customHeight="1">
       <c r="G807" s="16"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="7:7" ht="15.75" customHeight="1">
       <c r="G808" s="16"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="7:7" ht="15.75" customHeight="1">
       <c r="G809" s="16"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="7:7" ht="15.75" customHeight="1">
       <c r="G810" s="16"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="7:7" ht="15.75" customHeight="1">
       <c r="G811" s="16"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="7:7" ht="15.75" customHeight="1">
       <c r="G812" s="16"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="7:7" ht="15.75" customHeight="1">
       <c r="G813" s="16"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="7:7" ht="15.75" customHeight="1">
       <c r="G814" s="16"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="7:7" ht="15.75" customHeight="1">
       <c r="G815" s="16"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="7:7" ht="15.75" customHeight="1">
       <c r="G816" s="16"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="7:7" ht="15.75" customHeight="1">
       <c r="G817" s="16"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="7:7" ht="15.75" customHeight="1">
       <c r="G818" s="16"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="7:7" ht="15.75" customHeight="1">
       <c r="G819" s="16"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="7:7" ht="15.75" customHeight="1">
       <c r="G820" s="16"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="7:7" ht="15.75" customHeight="1">
       <c r="G821" s="16"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="7:7" ht="15.75" customHeight="1">
       <c r="G822" s="16"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="7:7" ht="15.75" customHeight="1">
       <c r="G823" s="16"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="7:7" ht="15.75" customHeight="1">
       <c r="G824" s="16"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="7:7" ht="15.75" customHeight="1">
       <c r="G825" s="16"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="7:7" ht="15.75" customHeight="1">
       <c r="G826" s="16"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="7:7" ht="15.75" customHeight="1">
       <c r="G827" s="16"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="7:7" ht="15.75" customHeight="1">
       <c r="G828" s="16"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="7:7" ht="15.75" customHeight="1">
       <c r="G829" s="16"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="7:7" ht="15.75" customHeight="1">
       <c r="G830" s="16"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="7:7" ht="15.75" customHeight="1">
       <c r="G831" s="16"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="7:7" ht="15.75" customHeight="1">
       <c r="G832" s="16"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="7:7" ht="15.75" customHeight="1">
       <c r="G833" s="16"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="7:7" ht="15.75" customHeight="1">
       <c r="G834" s="16"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="7:7" ht="15.75" customHeight="1">
       <c r="G835" s="16"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="7:7" ht="15.75" customHeight="1">
       <c r="G836" s="16"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="7:7" ht="15.75" customHeight="1">
       <c r="G837" s="16"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="7:7" ht="15.75" customHeight="1">
       <c r="G838" s="16"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="7:7" ht="15.75" customHeight="1">
       <c r="G839" s="16"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="7:7" ht="15.75" customHeight="1">
       <c r="G840" s="16"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="7:7" ht="15.75" customHeight="1">
       <c r="G841" s="16"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="7:7" ht="15.75" customHeight="1">
       <c r="G842" s="16"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="7:7" ht="15.75" customHeight="1">
       <c r="G843" s="16"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="7:7" ht="15.75" customHeight="1">
       <c r="G844" s="16"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="7:7" ht="15.75" customHeight="1">
       <c r="G845" s="16"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="7:7" ht="15.75" customHeight="1">
       <c r="G846" s="16"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="7:7" ht="15.75" customHeight="1">
       <c r="G847" s="16"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="7:7" ht="15.75" customHeight="1">
       <c r="G848" s="16"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="7:7" ht="15.75" customHeight="1">
       <c r="G849" s="16"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="7:7" ht="15.75" customHeight="1">
       <c r="G850" s="16"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="7:7" ht="15.75" customHeight="1">
       <c r="G851" s="16"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="7:7" ht="15.75" customHeight="1">
       <c r="G852" s="16"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="7:7" ht="15.75" customHeight="1">
       <c r="G853" s="16"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="7:7" ht="15.75" customHeight="1">
       <c r="G854" s="16"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="7:7" ht="15.75" customHeight="1">
       <c r="G855" s="16"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="7:7" ht="15.75" customHeight="1">
       <c r="G856" s="16"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="7:7" ht="15.75" customHeight="1">
       <c r="G857" s="16"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="7:7" ht="15.75" customHeight="1">
       <c r="G858" s="16"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="7:7" ht="15.75" customHeight="1">
       <c r="G859" s="16"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="7:7" ht="15.75" customHeight="1">
       <c r="G860" s="16"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="7:7" ht="15.75" customHeight="1">
       <c r="G861" s="16"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="7:7" ht="15.75" customHeight="1">
       <c r="G862" s="16"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="7:7" ht="15.75" customHeight="1">
       <c r="G863" s="16"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="7:7" ht="15.75" customHeight="1">
       <c r="G864" s="16"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="7:7" ht="15.75" customHeight="1">
       <c r="G865" s="16"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="7:7" ht="15.75" customHeight="1">
       <c r="G866" s="16"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="7:7" ht="15.75" customHeight="1">
       <c r="G867" s="16"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="7:7" ht="15.75" customHeight="1">
       <c r="G868" s="16"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="7:7" ht="15.75" customHeight="1">
       <c r="G869" s="16"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="7:7" ht="15.75" customHeight="1">
       <c r="G870" s="16"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="7:7" ht="15.75" customHeight="1">
       <c r="G871" s="16"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="7:7" ht="15.75" customHeight="1">
       <c r="G872" s="16"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="7:7" ht="15.75" customHeight="1">
       <c r="G873" s="16"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="7:7" ht="15.75" customHeight="1">
       <c r="G874" s="16"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="7:7" ht="15.75" customHeight="1">
       <c r="G875" s="16"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="7:7" ht="15.75" customHeight="1">
       <c r="G876" s="16"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="7:7" ht="15.75" customHeight="1">
       <c r="G877" s="16"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="7:7" ht="15.75" customHeight="1">
       <c r="G878" s="16"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="7:7" ht="15.75" customHeight="1">
       <c r="G879" s="16"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="7:7" ht="15.75" customHeight="1">
       <c r="G880" s="16"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="7:7" ht="15.75" customHeight="1">
       <c r="G881" s="16"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="7:7" ht="15.75" customHeight="1">
       <c r="G882" s="16"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="7:7" ht="15.75" customHeight="1">
       <c r="G883" s="16"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="7:7" ht="15.75" customHeight="1">
       <c r="G884" s="16"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="7:7" ht="15.75" customHeight="1">
       <c r="G885" s="16"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="7:7" ht="15.75" customHeight="1">
       <c r="G886" s="16"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="7:7" ht="15.75" customHeight="1">
       <c r="G887" s="16"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="7:7" ht="15.75" customHeight="1">
       <c r="G888" s="16"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="7:7" ht="15.75" customHeight="1">
       <c r="G889" s="16"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="7:7" ht="15.75" customHeight="1">
       <c r="G890" s="16"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="7:7" ht="15.75" customHeight="1">
       <c r="G891" s="16"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="7:7" ht="15.75" customHeight="1">
       <c r="G892" s="16"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="7:7" ht="15.75" customHeight="1">
       <c r="G893" s="16"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="7:7" ht="15.75" customHeight="1">
       <c r="G894" s="16"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="7:7" ht="15.75" customHeight="1">
       <c r="G895" s="16"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="7:7" ht="15.75" customHeight="1">
       <c r="G896" s="16"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="7:7" ht="15.75" customHeight="1">
       <c r="G897" s="16"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="7:7" ht="15.75" customHeight="1">
       <c r="G898" s="16"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="7:7" ht="15.75" customHeight="1">
       <c r="G899" s="16"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="7:7" ht="15.75" customHeight="1">
       <c r="G900" s="16"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="7:7" ht="15.75" customHeight="1">
       <c r="G901" s="16"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="7:7" ht="15.75" customHeight="1">
       <c r="G902" s="16"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="7:7" ht="15.75" customHeight="1">
       <c r="G903" s="16"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="7:7" ht="15.75" customHeight="1">
       <c r="G904" s="16"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="7:7" ht="15.75" customHeight="1">
       <c r="G905" s="16"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="7:7" ht="15.75" customHeight="1">
       <c r="G906" s="16"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="7:7" ht="15.75" customHeight="1">
       <c r="G907" s="16"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="7:7" ht="15.75" customHeight="1">
       <c r="G908" s="16"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="7:7" ht="15.75" customHeight="1">
       <c r="G909" s="16"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="7:7" ht="15.75" customHeight="1">
       <c r="G910" s="16"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="7:7" ht="15.75" customHeight="1">
       <c r="G911" s="16"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="7:7" ht="15.75" customHeight="1">
       <c r="G912" s="16"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="7:7" ht="15.75" customHeight="1">
       <c r="G913" s="16"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="7:7" ht="15.75" customHeight="1">
       <c r="G914" s="16"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="7:7" ht="15.75" customHeight="1">
       <c r="G915" s="16"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="7:7" ht="15.75" customHeight="1">
       <c r="G916" s="16"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="7:7" ht="15.75" customHeight="1">
       <c r="G917" s="16"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="7:7" ht="15.75" customHeight="1">
       <c r="G918" s="16"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="7:7" ht="15.75" customHeight="1">
       <c r="G919" s="16"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="7:7" ht="15.75" customHeight="1">
       <c r="G920" s="16"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="7:7" ht="15.75" customHeight="1">
       <c r="G921" s="16"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="7:7" ht="15.75" customHeight="1">
       <c r="G922" s="16"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="7:7" ht="15.75" customHeight="1">
       <c r="G923" s="16"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="7:7" ht="15.75" customHeight="1">
       <c r="G924" s="16"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="7:7" ht="15.75" customHeight="1">
       <c r="G925" s="16"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="7:7" ht="15.75" customHeight="1">
       <c r="G926" s="16"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="7:7" ht="15.75" customHeight="1">
       <c r="G927" s="16"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="7:7" ht="15.75" customHeight="1">
       <c r="G928" s="16"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="7:7" ht="15.75" customHeight="1">
       <c r="G929" s="16"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="7:7" ht="15.75" customHeight="1">
       <c r="G930" s="16"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="7:7" ht="15.75" customHeight="1">
       <c r="G931" s="16"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="7:7" ht="15.75" customHeight="1">
       <c r="G932" s="16"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="7:7" ht="15.75" customHeight="1">
       <c r="G933" s="16"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="7:7" ht="15.75" customHeight="1">
       <c r="G934" s="16"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="7:7" ht="15.75" customHeight="1">
       <c r="G935" s="16"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="7:7" ht="15.75" customHeight="1">
       <c r="G936" s="16"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="7:7" ht="15.75" customHeight="1">
       <c r="G937" s="16"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="7:7" ht="15.75" customHeight="1">
       <c r="G938" s="16"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="7:7" ht="15.75" customHeight="1">
       <c r="G939" s="16"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="7:7" ht="15.75" customHeight="1">
       <c r="G940" s="16"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="7:7" ht="15.75" customHeight="1">
       <c r="G941" s="16"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="7:7" ht="15.75" customHeight="1">
       <c r="G942" s="16"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="7:7" ht="15.75" customHeight="1">
       <c r="G943" s="16"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="7:7" ht="15.75" customHeight="1">
       <c r="G944" s="16"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="7:7" ht="15.75" customHeight="1">
       <c r="G945" s="16"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="7:7" ht="15.75" customHeight="1">
       <c r="G946" s="16"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="7:7" ht="15.75" customHeight="1">
       <c r="G947" s="16"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="7:7" ht="15.75" customHeight="1">
       <c r="G948" s="16"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="7:7" ht="15.75" customHeight="1">
       <c r="G949" s="16"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="7:7" ht="15.75" customHeight="1">
       <c r="G950" s="16"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="7:7" ht="15.75" customHeight="1">
       <c r="G951" s="16"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="7:7" ht="15.75" customHeight="1">
       <c r="G952" s="16"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="7:7" ht="15.75" customHeight="1">
       <c r="G953" s="16"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="7:7" ht="15.75" customHeight="1">
       <c r="G954" s="16"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="7:7" ht="15.75" customHeight="1">
       <c r="G955" s="16"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="7:7" ht="15.75" customHeight="1">
       <c r="G956" s="16"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="7:7" ht="15.75" customHeight="1">
       <c r="G957" s="16"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="7:7" ht="15.75" customHeight="1">
       <c r="G958" s="16"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="7:7" ht="15.75" customHeight="1">
       <c r="G959" s="16"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="7:7" ht="15.75" customHeight="1">
       <c r="G960" s="16"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="7:7" ht="15.75" customHeight="1">
       <c r="G961" s="16"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="7:7" ht="15.75" customHeight="1">
       <c r="G962" s="16"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="7:7" ht="15.75" customHeight="1">
       <c r="G963" s="16"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="7:7" ht="15.75" customHeight="1">
       <c r="G964" s="16"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="7:7" ht="15.75" customHeight="1">
       <c r="G965" s="16"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="7:7" ht="15.75" customHeight="1">
       <c r="G966" s="16"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="7:7" ht="15.75" customHeight="1">
       <c r="G967" s="16"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="7:7" ht="15.75" customHeight="1">
       <c r="G968" s="16"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="7:7" ht="15.75" customHeight="1">
       <c r="G969" s="16"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="7:7" ht="15.75" customHeight="1">
       <c r="G970" s="16"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="7:7" ht="15.75" customHeight="1">
       <c r="G971" s="16"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="7:7" ht="15.75" customHeight="1">
       <c r="G972" s="16"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="7:7" ht="15.75" customHeight="1">
       <c r="G973" s="16"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="7:7" ht="15.75" customHeight="1">
       <c r="G974" s="16"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="7:7" ht="15.75" customHeight="1">
       <c r="G975" s="16"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="7:7" ht="15.75" customHeight="1">
       <c r="G976" s="16"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="7:7" ht="15.75" customHeight="1">
       <c r="G977" s="16"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="7:7" ht="15.75" customHeight="1">
       <c r="G978" s="16"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="7:7" ht="15.75" customHeight="1">
       <c r="G979" s="16"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="7:7" ht="15.75" customHeight="1">
       <c r="G980" s="16"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="7:7" ht="15.75" customHeight="1">
       <c r="G981" s="16"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="7:7" ht="15.75" customHeight="1">
       <c r="G982" s="16"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="7:7" ht="15.75" customHeight="1">
       <c r="G983" s="16"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="7:7" ht="15.75" customHeight="1">
       <c r="G984" s="16"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="7:7" ht="15.75" customHeight="1">
       <c r="G985" s="16"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="7:7" ht="15.75" customHeight="1">
       <c r="G986" s="16"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="7:7" ht="15.75" customHeight="1">
       <c r="G987" s="16"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="7:7" ht="15.75" customHeight="1">
       <c r="G988" s="16"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="7:7" ht="15.75" customHeight="1">
       <c r="G989" s="16"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="7:7" ht="15.75" customHeight="1">
       <c r="G990" s="16"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="7:7" ht="15.75" customHeight="1">
       <c r="G991" s="16"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="7:7" ht="15.75" customHeight="1">
       <c r="G992" s="16"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="7:7" ht="15.75" customHeight="1">
       <c r="G993" s="16"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="7:7" ht="15.75" customHeight="1">
       <c r="G994" s="16"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="7:7" ht="15.75" customHeight="1">
       <c r="G995" s="16"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="7:7" ht="15.75" customHeight="1">
       <c r="G996" s="16"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="7:7" ht="15.75" customHeight="1">
       <c r="G997" s="16"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="7:7" ht="15.75" customHeight="1">
       <c r="G998" s="16"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="7:7" ht="15.75" customHeight="1">
       <c r="G999" s="16"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="7:7" ht="15.75" customHeight="1">
       <c r="G1000" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$I$152"/>
+  <autoFilter ref="A1:I152"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" stopIfTrue="1" operator="equal">
       <formula>"調整後"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" stopIfTrue="1" operator="equal">
       <formula>"再次調整"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="2" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" stopIfTrue="1" operator="equal">
       <formula>"延長"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" stopIfTrue="1" operator="equal">
       <formula>"再次延長"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" stopIfTrue="1" operator="equal">
       <formula>"加碼"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="4" priority="6" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="6" stopIfTrue="1" operator="equal">
       <formula>"獨家加碼"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="4" priority="7" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="equal">
       <formula>"搶先開跑"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="5" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="equal">
       <formula>"取消"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8803,38 +9277,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="7" priority="10" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="equal">
       <formula>"長期"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="0" priority="11" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="equal">
       <formula>"日期調整"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="6" priority="12" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="equal">
       <formula>"系統調整"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="1" priority="13" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="equal">
       <formula>"原訂(後改)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="2" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="14" stopIfTrue="1" operator="equal">
       <formula>"原訂(後延長)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="cellIs" dxfId="5" priority="15" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="15" stopIfTrue="1" operator="equal">
       <formula>"原訂(後取消)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/AIRSPACE_線下通路_行銷排程_含甘特圖_2025-2026.xlsx
+++ b/data/AIRSPACE_線下通路_行銷排程_含甘特圖_2025-2026.xlsx
@@ -12,12 +12,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">行銷排程!$A$1:$I$151</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="460">
   <si>
     <t>年度</t>
   </si>
@@ -1288,12 +1288,6 @@
     <t>如消費滿2500且加購手機支架，則KEY入兩個贈品，系統會自動判斷一個為加購價/一個為贈品;請務必確實銷貨，若有漏KEY，可另外成立一單備註補XX單之贈品;贈不織布袋及手機鍊僅販售CA及PLUS及IP店櫃適用活動，贈手機支架全體正價店適用</t>
   </si>
   <si>
-    <t>6/4-6/21</t>
-  </si>
-  <si>
-    <t>2026/06/03郵件</t>
-  </si>
-  <si>
     <t>2026/06/10郵件</t>
   </si>
   <si>
@@ -1321,9 +1315,6 @@
     <t>2026/06/18郵件</t>
   </si>
   <si>
-    <t>8/1起 官網下單門市取貨獨家 凡於官網下單門市取貨者 當日到店取貨且在門市不限消費金額現折100 POS操作：輸入會員條碼→再輸入折扣碼【PICKUP100】</t>
-  </si>
-  <si>
     <t>2026/06/30郵件</t>
   </si>
   <si>
@@ -1336,9 +1327,6 @@
     <t>7/9-7/26</t>
   </si>
   <si>
-    <t>7/9-7/26 部分店櫃適用 一般會員/過路客滿3200贈玩總行李吊牌 VIP/SVIP滿2500贈玩總行李吊牌 左營新光店、台中漢神店、嘉義秀泰店、新台南FOCUS店 [image: image.png]</t>
-  </si>
-  <si>
     <t>台中漢神</t>
   </si>
   <si>
@@ -1348,37 +1336,75 @@
     <t>7/6-7/12</t>
   </si>
   <si>
-    <t>7/6-7/12 IP專賣店櫃獨家 消費DINOTAENG商品即贈DINOTAENG滑鼠墊 全館滿2500贈DINOTAENG手機鍊 [image: image.png]</t>
-  </si>
-  <si>
-    <t>7/13-7/26 IP專賣店櫃獨家 消費DINOTAENG商品即贈DINOTAENG手機支架 [image: image.png]</t>
-  </si>
-  <si>
-    <t>7/9-7/12</t>
-  </si>
-  <si>
     <t>會員專屬</t>
   </si>
   <si>
-    <t>情境說明 若於7/9-7/12 之間VIP/SVIP消費滿2500</t>
-  </si>
-  <si>
     <t>適用門市/通路</t>
   </si>
   <si>
-    <t>適用百貨 新莊宏匯/桃園台茂/桃園大江/桃園統領/新光中港/夢時代/新光左營</t>
+    <t>7/13-7/19</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>全館商品三件以上85折</t>
+    <t>08/10-08/23</t>
+  </si>
+  <si>
+    <t>滿2500贈袋鼠購物袋組 (不分會員) 滿3200贈玩總行李吊牌 (一般及非會員) 滿2500贈玩總行李吊牌 (SVIP及VIP)</t>
+  </si>
+  <si>
+    <t>滿2500贈烤焦KT絨毛吊飾 (不分會員) 滿3200贈玩總行李吊牌 (一般及非會員) 滿2500贈玩總行李吊牌 (SVIP及VIP)</t>
+  </si>
+  <si>
+    <t>08/10-08/16</t>
+  </si>
+  <si>
+    <t>08/10-08/16 門網同步 (IP正價店不適用) 全館三件85折、滿3800再折380</t>
+  </si>
+  <si>
+    <t>IP商品/當年度KOL聯名款/甜甜價/體驗價/組合價(包含買單件)*不列入三件折扣;但可湊滿額折價</t>
+  </si>
+  <si>
+    <t>08/17-08/30</t>
+  </si>
+  <si>
+    <t>08/21-08/24</t>
+  </si>
+  <si>
+    <t>08/24-09/13</t>
+  </si>
+  <si>
+    <t>IP專賣店活動 滿1800贈$150紅利金 (8/31、9/7、9/14匯入點數) 滿2500贈烤焦KT絨毛吊飾 (不分會員) 滿3200贈玩總行李吊牌 (一般及非會員) 滿2500贈玩總行李吊牌 (SVIP及VIP)</t>
+  </si>
+  <si>
+    <t>08/24-09/13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>部分百貨提前開跑</t>
+    <t>買當周新品加倍贈紅利點數</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7/13-7/19</t>
+    <t>08/17-09/13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08/17-08/30 春夏鞋款全館單件65折 (排除聯名款) 大碼商品全館單件85折</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08/21-08/24 &amp; 08/28-08/30 門網同步加碼 精選泳裝單件39折</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/13-7/26 IP專賣店櫃獨家 消費DINOTAENG商品即贈DINOTAENG手機支架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/6-7/12 IP專賣店櫃獨家 消費DINOTAENG商品即贈DINOTAENG滑鼠墊 全館滿2500贈DINOTAENG手機鍊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/9-7/26 部分店櫃適用 一般會員/過路客滿3200贈玩總行李吊牌 VIP/SVIP滿2500贈玩總行李吊牌 左營新光店、台中漢神店、嘉義秀泰店、新台南FOCUS店</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1386,10 +1412,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="m/d"/>
+    <numFmt numFmtId="181" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1414,13 +1441,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1556,14 +1576,134 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="30">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEEBF7"/>
+          <bgColor rgb="FFDEEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDEDED"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDEDED"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEEBF7"/>
+          <bgColor rgb="FFDEEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1896,12 +2036,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I997"/>
+  <dimension ref="A1:I982"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="6" style="4" customWidth="1"/>
     <col min="3" max="4" width="16" style="4" customWidth="1"/>
-    <col min="5" max="5" width="61.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="255.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" style="4" customWidth="1"/>
     <col min="7" max="7" width="14" style="4" customWidth="1"/>
     <col min="8" max="8" width="62.7109375" style="4" customWidth="1"/>
@@ -1927,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -5909,7 +6049,7 @@
         <v>396</v>
       </c>
       <c r="I138" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6151,14 +6291,14 @@
       <c r="B147" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C147" s="16" t="s">
-        <v>426</v>
+      <c r="C147" s="15" t="s">
+        <v>424</v>
       </c>
       <c r="D147" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F147" s="15" t="s">
         <v>18</v>
@@ -6167,10 +6307,10 @@
         <v>19</v>
       </c>
       <c r="H147" s="15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I147" s="15" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6180,7 +6320,7 @@
       <c r="B148" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C148" s="16" t="s">
+      <c r="C148" s="15" t="s">
         <v>418</v>
       </c>
       <c r="D148" s="15" t="s">
@@ -6196,10 +6336,10 @@
         <v>19</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I148" s="15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6209,7 +6349,7 @@
       <c r="B149" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C149" s="16" t="s">
+      <c r="C149" s="15" t="s">
         <v>420</v>
       </c>
       <c r="D149" s="15" t="s">
@@ -6238,14 +6378,14 @@
       <c r="B150" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C150" s="16" t="s">
-        <v>431</v>
+      <c r="C150" s="15" t="s">
+        <v>429</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>397</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>12</v>
@@ -6257,7 +6397,7 @@
         <v>13</v>
       </c>
       <c r="I150" s="15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6267,14 +6407,14 @@
       <c r="B151" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C151" s="16" t="s">
-        <v>431</v>
+      <c r="C151" s="15" t="s">
+        <v>429</v>
       </c>
       <c r="D151" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F151" s="15" t="s">
         <v>118</v>
@@ -6286,7 +6426,7 @@
         <v>13</v>
       </c>
       <c r="I151" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6296,26 +6436,26 @@
       <c r="B152" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C152" s="16" t="s">
-        <v>423</v>
+      <c r="C152" s="15" t="s">
+        <v>415</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>451</v>
+        <v>12</v>
       </c>
       <c r="G152" s="15" t="s">
         <v>19</v>
       </c>
       <c r="H152" s="15" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="I152" s="15" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6323,10 +6463,10 @@
         <v>2026</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C153" s="16" t="s">
-        <v>415</v>
+        <v>122</v>
+      </c>
+      <c r="C153" s="15" t="s">
+        <v>441</v>
       </c>
       <c r="D153" s="15" t="s">
         <v>22</v>
@@ -6340,11 +6480,9 @@
       <c r="G153" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H153" s="15" t="s">
-        <v>417</v>
-      </c>
+      <c r="H153" s="15"/>
       <c r="I153" s="15" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6354,14 +6492,14 @@
       <c r="B154" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C154" s="16" t="s">
-        <v>452</v>
+      <c r="C154" s="15" t="s">
+        <v>434</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E154" s="16" t="s">
-        <v>416</v>
+        <v>397</v>
+      </c>
+      <c r="E154" s="15" t="s">
+        <v>457</v>
       </c>
       <c r="F154" s="15" t="s">
         <v>12</v>
@@ -6369,9 +6507,11 @@
       <c r="G154" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H154" s="15"/>
+      <c r="H154" s="15" t="s">
+        <v>13</v>
+      </c>
       <c r="I154" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6382,13 +6522,13 @@
         <v>122</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>397</v>
+        <v>95</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="F155" s="15" t="s">
         <v>12</v>
@@ -6400,7 +6540,7 @@
         <v>13</v>
       </c>
       <c r="I155" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6411,83 +6551,80 @@
         <v>122</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E156" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="F156" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="G156" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="I156" s="15" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E158" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="F156" s="15" t="s">
+      <c r="F158" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G156" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H156" s="15" t="s">
+      <c r="G158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="I156" s="15" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15">
-        <v>2026</v>
-      </c>
-      <c r="B157" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C157" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="E157" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="F157" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G157" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H157" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I157" s="15" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="15">
-        <v>2026</v>
-      </c>
-      <c r="B158" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C158" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E158" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="F158" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="G158" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H158" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="I158" s="15" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6498,13 +6635,13 @@
         <v>135</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>137</v>
+        <v>452</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>390</v>
+        <v>95</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>12</v>
@@ -6513,10 +6650,7 @@
         <v>19</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="I159" s="4" t="s">
-        <v>392</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6527,13 +6661,13 @@
         <v>135</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>137</v>
+        <v>445</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>390</v>
+        <v>16</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>391</v>
+        <v>446</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>12</v>
@@ -6542,13 +6676,10 @@
         <v>19</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="I160" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>2026</v>
       </c>
@@ -6556,42 +6687,114 @@
         <v>135</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>137</v>
+        <v>448</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>390</v>
+        <v>22</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="I161" s="4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7398,21 +7601,6 @@
     <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:I151">
     <sortState ref="A2:I164">
@@ -7420,77 +7608,77 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="14" priority="1" stopIfTrue="1" operator="equal">
       <formula>"調整後"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="13" priority="2" stopIfTrue="1" operator="equal">
       <formula>"再次調整"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="12" priority="3" stopIfTrue="1" operator="equal">
       <formula>"延長"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="11" priority="4" stopIfTrue="1" operator="equal">
       <formula>"再次延長"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="10" priority="5" stopIfTrue="1" operator="equal">
       <formula>"加碼"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="9" priority="6" stopIfTrue="1" operator="equal">
       <formula>"獨家加碼"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="equal">
       <formula>"搶先開跑"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="equal">
       <formula>"取消"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="equal">
       <formula>"補充"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="equal">
       <formula>"長期"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="equal">
       <formula>"日期調整"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="equal">
       <formula>"系統調整"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="equal">
       <formula>"原訂(後改)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="1" priority="14" stopIfTrue="1" operator="equal">
       <formula>"原訂(後延長)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G997">
+  <conditionalFormatting sqref="G2:G982">
     <cfRule type="cellIs" dxfId="0" priority="15" stopIfTrue="1" operator="equal">
       <formula>"原訂(後取消)"</formula>
     </cfRule>
